--- a/research/traditional_assets/database/data/thailand/thailand_education.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_education.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09439425834771148</v>
+        <v>0.09424146983101606</v>
       </c>
       <c r="C2">
-        <v>837.2181764557916</v>
+        <v>831.3974728872871</v>
       </c>
       <c r="D2">
-        <v>807.6181764557916</v>
+        <v>810.1654728872871</v>
       </c>
       <c r="E2">
-        <v>-15.2</v>
+        <v>-6.831999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.368</v>
       </c>
       <c r="G2">
         <v>29.6</v>
@@ -1579,28 +1579,28 @@
         <v>25.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4209104</v>
       </c>
       <c r="N2">
-        <v>25.9</v>
+        <v>25.4790896</v>
       </c>
       <c r="O2">
-        <v>5.18</v>
+        <v>5.09581792</v>
       </c>
       <c r="P2">
-        <v>20.72</v>
+        <v>20.38327168</v>
       </c>
       <c r="Q2">
-        <v>26.12</v>
+        <v>25.78327168</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09439425834771148</v>
+        <v>0.09478693922324855</v>
       </c>
       <c r="T2">
-        <v>0.7517377218129921</v>
+        <v>0.7578123700700669</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>61.53328594399187</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09424146983101606</v>
+        <v>0.09408868131432063</v>
       </c>
       <c r="C3">
-        <v>831.3974728872871</v>
+        <v>825.5928889407213</v>
       </c>
       <c r="D3">
-        <v>810.1654728872871</v>
+        <v>812.7288889407213</v>
       </c>
       <c r="E3">
-        <v>-6.831999999999999</v>
+        <v>1.536000000000001</v>
       </c>
       <c r="F3">
-        <v>8.368</v>
+        <v>16.736</v>
       </c>
       <c r="G3">
         <v>29.6</v>
@@ -1661,28 +1661,28 @@
         <v>25.9</v>
       </c>
       <c r="M3">
-        <v>0.4209104</v>
+        <v>0.8418208</v>
       </c>
       <c r="N3">
-        <v>25.4790896</v>
+        <v>25.0581792</v>
       </c>
       <c r="O3">
-        <v>5.09581792</v>
+        <v>5.01163584</v>
       </c>
       <c r="P3">
-        <v>20.38327168</v>
+        <v>20.04654336</v>
       </c>
       <c r="Q3">
-        <v>25.78327168</v>
+        <v>25.44654336</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09478693922324855</v>
+        <v>0.09518763399420474</v>
       </c>
       <c r="T3">
-        <v>0.7578123700700669</v>
+        <v>0.7640109907405512</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>61.53328594399187</v>
+        <v>30.76664297199594</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09408868131432063</v>
+        <v>0.09393589279762522</v>
       </c>
       <c r="C4">
-        <v>825.5928889407213</v>
+        <v>819.8045781123509</v>
       </c>
       <c r="D4">
-        <v>812.7288889407213</v>
+        <v>815.3085781123509</v>
       </c>
       <c r="E4">
-        <v>1.536000000000001</v>
+        <v>9.904000000000003</v>
       </c>
       <c r="F4">
-        <v>16.736</v>
+        <v>25.104</v>
       </c>
       <c r="G4">
         <v>29.6</v>
@@ -1743,28 +1743,28 @@
         <v>25.9</v>
       </c>
       <c r="M4">
-        <v>0.8418208</v>
+        <v>1.2627312</v>
       </c>
       <c r="N4">
-        <v>25.0581792</v>
+        <v>24.6372688</v>
       </c>
       <c r="O4">
-        <v>5.01163584</v>
+        <v>4.92745376</v>
       </c>
       <c r="P4">
-        <v>20.04654336</v>
+        <v>19.70981504</v>
       </c>
       <c r="Q4">
-        <v>25.44654336</v>
+        <v>25.10981504</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09518763399420474</v>
+        <v>0.09559659051301569</v>
       </c>
       <c r="T4">
-        <v>0.7640109907405512</v>
+        <v>0.7703374180227981</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.76664297199594</v>
+        <v>20.51109531466395</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09393589279762522</v>
+        <v>0.0937831042809298</v>
       </c>
       <c r="C5">
-        <v>819.8045781123509</v>
+        <v>814.0326958534941</v>
       </c>
       <c r="D5">
-        <v>815.3085781123509</v>
+        <v>817.9046958534941</v>
       </c>
       <c r="E5">
-        <v>9.904000000000003</v>
+        <v>18.272</v>
       </c>
       <c r="F5">
-        <v>25.104</v>
+        <v>33.472</v>
       </c>
       <c r="G5">
         <v>29.6</v>
@@ -1825,28 +1825,28 @@
         <v>25.9</v>
       </c>
       <c r="M5">
-        <v>1.2627312</v>
+        <v>1.6836416</v>
       </c>
       <c r="N5">
-        <v>24.6372688</v>
+        <v>24.2163584</v>
       </c>
       <c r="O5">
-        <v>4.92745376</v>
+        <v>4.84327168</v>
       </c>
       <c r="P5">
-        <v>19.70981504</v>
+        <v>19.37308672</v>
       </c>
       <c r="Q5">
-        <v>25.10981504</v>
+        <v>24.77308672</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09559659051301569</v>
+        <v>0.09601406695930187</v>
       </c>
       <c r="T5">
-        <v>0.7703374180227981</v>
+        <v>0.7767956458734253</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.51109531466395</v>
+        <v>15.38332148599797</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0937831042809298</v>
+        <v>0.09369031576423437</v>
       </c>
       <c r="C6">
-        <v>814.0326958534941</v>
+        <v>807.2494037911091</v>
       </c>
       <c r="D6">
-        <v>817.9046958534941</v>
+        <v>819.4894037911091</v>
       </c>
       <c r="E6">
-        <v>18.272</v>
+        <v>26.64</v>
       </c>
       <c r="F6">
-        <v>33.472</v>
+        <v>41.84</v>
       </c>
       <c r="G6">
         <v>29.6</v>
@@ -1907,45 +1907,45 @@
         <v>25.9</v>
       </c>
       <c r="M6">
-        <v>1.6836416</v>
+        <v>2.167312</v>
       </c>
       <c r="N6">
-        <v>24.2163584</v>
+        <v>23.732688</v>
       </c>
       <c r="O6">
-        <v>4.84327168</v>
+        <v>4.7465376</v>
       </c>
       <c r="P6">
-        <v>19.37308672</v>
+        <v>18.9861504</v>
       </c>
       <c r="Q6">
-        <v>24.77308672</v>
+        <v>24.3861504</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09601406695930187</v>
+        <v>0.0964403323834046</v>
       </c>
       <c r="T6">
-        <v>0.7767956458734253</v>
+        <v>0.7833898364156444</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>15.38332148599797</v>
+        <v>11.95028680688336</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09369031576423437</v>
+        <v>0.09354952724753895</v>
       </c>
       <c r="C7">
-        <v>807.2494037911091</v>
+        <v>801.2976517470154</v>
       </c>
       <c r="D7">
-        <v>819.4894037911091</v>
+        <v>821.9056517470153</v>
       </c>
       <c r="E7">
-        <v>26.64</v>
+        <v>35.00800000000001</v>
       </c>
       <c r="F7">
-        <v>41.84</v>
+        <v>50.20800000000001</v>
       </c>
       <c r="G7">
         <v>29.6</v>
@@ -1989,28 +1989,28 @@
         <v>25.9</v>
       </c>
       <c r="M7">
-        <v>2.167312</v>
+        <v>2.6007744</v>
       </c>
       <c r="N7">
-        <v>23.732688</v>
+        <v>23.2992256</v>
       </c>
       <c r="O7">
-        <v>4.7465376</v>
+        <v>4.65984512</v>
       </c>
       <c r="P7">
-        <v>18.9861504</v>
+        <v>18.63938048</v>
       </c>
       <c r="Q7">
-        <v>24.3861504</v>
+        <v>24.03938048</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0964403323834046</v>
+        <v>0.09687566728461591</v>
       </c>
       <c r="T7">
-        <v>0.7833898364156444</v>
+        <v>0.790124328884294</v>
       </c>
       <c r="U7">
         <v>0.0518</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>11.95028680688336</v>
+        <v>9.95857233906947</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09354952724753895</v>
+        <v>0.09350393873084353</v>
       </c>
       <c r="C8">
-        <v>801.2976517470154</v>
+        <v>793.7151101498978</v>
       </c>
       <c r="D8">
-        <v>821.9056517470153</v>
+        <v>822.6911101498978</v>
       </c>
       <c r="E8">
-        <v>35.00800000000001</v>
+        <v>43.376</v>
       </c>
       <c r="F8">
-        <v>50.20800000000001</v>
+        <v>58.576</v>
       </c>
       <c r="G8">
         <v>29.6</v>
@@ -2071,45 +2071,45 @@
         <v>25.9</v>
       </c>
       <c r="M8">
-        <v>2.6007744</v>
+        <v>3.133816</v>
       </c>
       <c r="N8">
-        <v>23.2992256</v>
+        <v>22.766184</v>
       </c>
       <c r="O8">
-        <v>4.65984512</v>
+        <v>4.5532368</v>
       </c>
       <c r="P8">
-        <v>18.63938048</v>
+        <v>18.2129472</v>
       </c>
       <c r="Q8">
-        <v>24.03938048</v>
+        <v>23.6129472</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09687566728461591</v>
+        <v>0.09732036422671347</v>
       </c>
       <c r="T8">
-        <v>0.790124328884294</v>
+        <v>0.7970036491479681</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>9.95857233906947</v>
+        <v>8.26468433373242</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09350393873084352</v>
+        <v>0.09342795021414811</v>
       </c>
       <c r="C9">
-        <v>793.7151101498981</v>
+        <v>786.6596813791386</v>
       </c>
       <c r="D9">
-        <v>822.6911101498981</v>
+        <v>824.0036813791386</v>
       </c>
       <c r="E9">
-        <v>43.376</v>
+        <v>51.744</v>
       </c>
       <c r="F9">
-        <v>58.57600000000001</v>
+        <v>66.944</v>
       </c>
       <c r="G9">
         <v>29.6</v>
@@ -2153,45 +2153,45 @@
         <v>25.9</v>
       </c>
       <c r="M9">
-        <v>3.133816</v>
+        <v>3.6350592</v>
       </c>
       <c r="N9">
-        <v>22.766184</v>
+        <v>22.2649408</v>
       </c>
       <c r="O9">
-        <v>4.5532368</v>
+        <v>4.452988159999999</v>
       </c>
       <c r="P9">
-        <v>18.2129472</v>
+        <v>17.81195264</v>
       </c>
       <c r="Q9">
-        <v>23.6129472</v>
+        <v>23.21195264</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09732036422671347</v>
+        <v>0.09777472849363925</v>
       </c>
       <c r="T9">
-        <v>0.7970036491479681</v>
+        <v>0.8040325198521568</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.264684333732419</v>
+        <v>7.125055900052466</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09342795021414811</v>
+        <v>0.09330716169745268</v>
       </c>
       <c r="C10">
-        <v>786.6596813791386</v>
+        <v>780.3867377636731</v>
       </c>
       <c r="D10">
-        <v>824.0036813791386</v>
+        <v>826.0987377636731</v>
       </c>
       <c r="E10">
-        <v>51.744</v>
+        <v>60.11199999999999</v>
       </c>
       <c r="F10">
-        <v>66.944</v>
+        <v>75.312</v>
       </c>
       <c r="G10">
         <v>29.6</v>
@@ -2235,28 +2235,28 @@
         <v>25.9</v>
       </c>
       <c r="M10">
-        <v>3.6350592</v>
+        <v>4.0894416</v>
       </c>
       <c r="N10">
-        <v>22.2649408</v>
+        <v>21.8105584</v>
       </c>
       <c r="O10">
-        <v>4.452988159999999</v>
+        <v>4.36211168</v>
       </c>
       <c r="P10">
-        <v>17.81195264</v>
+        <v>17.44844672</v>
       </c>
       <c r="Q10">
-        <v>23.21195264</v>
+        <v>22.84844672</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09777472849363925</v>
+        <v>0.09823907878840954</v>
       </c>
       <c r="T10">
-        <v>0.8040325198521568</v>
+        <v>0.8112158712311629</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.125055900052466</v>
+        <v>6.333383022268859</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09330716169745268</v>
+        <v>0.09326637318075726</v>
       </c>
       <c r="C11">
-        <v>780.3867377636731</v>
+        <v>772.7286159342473</v>
       </c>
       <c r="D11">
-        <v>826.0987377636731</v>
+        <v>826.8086159342472</v>
       </c>
       <c r="E11">
-        <v>60.11199999999999</v>
+        <v>68.48</v>
       </c>
       <c r="F11">
-        <v>75.312</v>
+        <v>83.68000000000001</v>
       </c>
       <c r="G11">
         <v>29.6</v>
@@ -2317,45 +2317,45 @@
         <v>25.9</v>
       </c>
       <c r="M11">
-        <v>4.0894416</v>
+        <v>4.627504000000001</v>
       </c>
       <c r="N11">
-        <v>21.8105584</v>
+        <v>21.272496</v>
       </c>
       <c r="O11">
-        <v>4.36211168</v>
+        <v>4.2544992</v>
       </c>
       <c r="P11">
-        <v>17.44844672</v>
+        <v>17.0179968</v>
       </c>
       <c r="Q11">
-        <v>22.84844672</v>
+        <v>22.4179968</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09823907878840954</v>
+        <v>0.09871374797861918</v>
       </c>
       <c r="T11">
-        <v>0.8112158712311629</v>
+        <v>0.8185588526408136</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.333383022268859</v>
+        <v>5.596969770312461</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09326637318075726</v>
+        <v>0.09315358466406184</v>
       </c>
       <c r="C12">
-        <v>772.7286159342473</v>
+        <v>766.3299392292793</v>
       </c>
       <c r="D12">
-        <v>826.8086159342472</v>
+        <v>828.7779392292792</v>
       </c>
       <c r="E12">
-        <v>68.48</v>
+        <v>76.848</v>
       </c>
       <c r="F12">
-        <v>83.68000000000001</v>
+        <v>92.048</v>
       </c>
       <c r="G12">
         <v>29.6</v>
@@ -2399,28 +2399,28 @@
         <v>25.9</v>
       </c>
       <c r="M12">
-        <v>4.627504000000001</v>
+        <v>5.0902544</v>
       </c>
       <c r="N12">
-        <v>21.272496</v>
+        <v>20.8097456</v>
       </c>
       <c r="O12">
-        <v>4.2544992</v>
+        <v>4.16194912</v>
       </c>
       <c r="P12">
-        <v>17.0179968</v>
+        <v>16.64779648</v>
       </c>
       <c r="Q12">
-        <v>22.4179968</v>
+        <v>22.04779648</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09871374797861918</v>
+        <v>0.0991990838922043</v>
       </c>
       <c r="T12">
-        <v>0.8185588526408137</v>
+        <v>0.8260668448686588</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.596969770312461</v>
+        <v>5.088154336647693</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09315358466406184</v>
+        <v>0.09304079614736642</v>
       </c>
       <c r="C13">
-        <v>766.3299392292793</v>
+        <v>759.9406661360816</v>
       </c>
       <c r="D13">
-        <v>828.7779392292792</v>
+        <v>830.7566661360817</v>
       </c>
       <c r="E13">
-        <v>76.848</v>
+        <v>85.21600000000001</v>
       </c>
       <c r="F13">
-        <v>92.048</v>
+        <v>100.416</v>
       </c>
       <c r="G13">
         <v>29.6</v>
@@ -2481,28 +2481,28 @@
         <v>25.9</v>
       </c>
       <c r="M13">
-        <v>5.0902544</v>
+        <v>5.553004800000001</v>
       </c>
       <c r="N13">
-        <v>20.8097456</v>
+        <v>20.3469952</v>
       </c>
       <c r="O13">
-        <v>4.16194912</v>
+        <v>4.06939904</v>
       </c>
       <c r="P13">
-        <v>16.64779648</v>
+        <v>16.27759616</v>
       </c>
       <c r="Q13">
-        <v>22.04779648</v>
+        <v>21.67759616</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0991990838922043</v>
+        <v>0.09969545016746184</v>
       </c>
       <c r="T13">
-        <v>0.8260668448686588</v>
+        <v>0.8337454732835005</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.088154336647693</v>
+        <v>4.664141475260385</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09304079614736642</v>
+        <v>0.09318800763067098</v>
       </c>
       <c r="C14">
-        <v>759.9406661360816</v>
+        <v>748.991909375</v>
       </c>
       <c r="D14">
-        <v>830.7566661360817</v>
+        <v>828.1759093749999</v>
       </c>
       <c r="E14">
-        <v>85.21600000000001</v>
+        <v>93.584</v>
       </c>
       <c r="F14">
-        <v>100.416</v>
+        <v>108.784</v>
       </c>
       <c r="G14">
         <v>29.6</v>
@@ -2563,45 +2563,45 @@
         <v>25.9</v>
       </c>
       <c r="M14">
-        <v>5.553004800000001</v>
+        <v>6.287715200000001</v>
       </c>
       <c r="N14">
-        <v>20.3469952</v>
+        <v>19.6122848</v>
       </c>
       <c r="O14">
-        <v>4.06939904</v>
+        <v>3.92245696</v>
       </c>
       <c r="P14">
-        <v>16.27759616</v>
+        <v>15.68982784</v>
       </c>
       <c r="Q14">
-        <v>21.67759616</v>
+        <v>21.08982784</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09969545016746184</v>
+        <v>0.1002032271616908</v>
       </c>
       <c r="T14">
-        <v>0.8337454732835005</v>
+        <v>0.8416006218917865</v>
       </c>
       <c r="U14">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.664141475260385</v>
+        <v>4.119143309798764</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09318800763067098</v>
+        <v>0.09348721911397556</v>
       </c>
       <c r="C15">
-        <v>748.991909375</v>
+        <v>735.4275538968379</v>
       </c>
       <c r="D15">
-        <v>828.1759093749999</v>
+        <v>822.979553896838</v>
       </c>
       <c r="E15">
-        <v>93.584</v>
+        <v>101.952</v>
       </c>
       <c r="F15">
-        <v>108.784</v>
+        <v>117.152</v>
       </c>
       <c r="G15">
         <v>29.6</v>
@@ -2645,45 +2645,45 @@
         <v>25.9</v>
       </c>
       <c r="M15">
-        <v>6.287715200000001</v>
+        <v>7.181417600000001</v>
       </c>
       <c r="N15">
-        <v>19.6122848</v>
+        <v>18.7185824</v>
       </c>
       <c r="O15">
-        <v>3.92245696</v>
+        <v>3.743716479999999</v>
       </c>
       <c r="P15">
-        <v>15.68982784</v>
+        <v>14.97486592</v>
       </c>
       <c r="Q15">
-        <v>21.08982784</v>
+        <v>20.37486592</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1002032271616908</v>
+        <v>0.1007228129232274</v>
       </c>
       <c r="T15">
-        <v>0.8416006218917865</v>
+        <v>0.8496384483746842</v>
       </c>
       <c r="U15">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.119143309798764</v>
+        <v>3.60653027613935</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09348721911397556</v>
+        <v>0.09375843059728013</v>
       </c>
       <c r="C16">
-        <v>735.4275538968379</v>
+        <v>722.4054919777569</v>
       </c>
       <c r="D16">
-        <v>822.979553896838</v>
+        <v>818.3254919777569</v>
       </c>
       <c r="E16">
-        <v>101.952</v>
+        <v>110.32</v>
       </c>
       <c r="F16">
-        <v>117.152</v>
+        <v>125.52</v>
       </c>
       <c r="G16">
         <v>29.6</v>
@@ -2727,45 +2727,45 @@
         <v>25.9</v>
       </c>
       <c r="M16">
-        <v>7.181417600000001</v>
+        <v>8.045832000000003</v>
       </c>
       <c r="N16">
-        <v>18.7185824</v>
+        <v>17.85416799999999</v>
       </c>
       <c r="O16">
-        <v>3.743716479999999</v>
+        <v>3.570833599999999</v>
       </c>
       <c r="P16">
-        <v>14.97486592</v>
+        <v>14.2833344</v>
       </c>
       <c r="Q16">
-        <v>20.37486592</v>
+        <v>19.6833344</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1007228129232274</v>
+        <v>0.1012546242320943</v>
       </c>
       <c r="T16">
-        <v>0.8496384483746842</v>
+        <v>0.857865400186591</v>
       </c>
       <c r="U16">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.60653027613935</v>
+        <v>3.219058016622767</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09375843059728013</v>
+        <v>0.0937160420805847</v>
       </c>
       <c r="C17">
-        <v>722.4054919777569</v>
+        <v>714.7614166232995</v>
       </c>
       <c r="D17">
-        <v>818.3254919777569</v>
+        <v>819.0494166232995</v>
       </c>
       <c r="E17">
-        <v>110.32</v>
+        <v>118.688</v>
       </c>
       <c r="F17">
-        <v>125.52</v>
+        <v>133.888</v>
       </c>
       <c r="G17">
         <v>29.6</v>
@@ -2809,28 +2809,28 @@
         <v>25.9</v>
       </c>
       <c r="M17">
-        <v>8.045832000000001</v>
+        <v>8.582220800000002</v>
       </c>
       <c r="N17">
-        <v>17.854168</v>
+        <v>17.3177792</v>
       </c>
       <c r="O17">
-        <v>3.5708336</v>
+        <v>3.46355584</v>
       </c>
       <c r="P17">
-        <v>14.2833344</v>
+        <v>13.85422336</v>
       </c>
       <c r="Q17">
-        <v>19.6833344</v>
+        <v>19.25422336</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1012546242320943</v>
+        <v>0.1017990977149818</v>
       </c>
       <c r="T17">
-        <v>0.857865400186591</v>
+        <v>0.8662882318035433</v>
       </c>
       <c r="U17">
         <v>0.0641</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.219058016622768</v>
+        <v>3.017866890583844</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0937160420805847</v>
+        <v>0.09473445356388929</v>
       </c>
       <c r="C18">
-        <v>714.7614166232995</v>
+        <v>689.3475671137296</v>
       </c>
       <c r="D18">
-        <v>819.0494166232995</v>
+        <v>802.0035671137297</v>
       </c>
       <c r="E18">
-        <v>118.688</v>
+        <v>127.056</v>
       </c>
       <c r="F18">
-        <v>133.888</v>
+        <v>142.256</v>
       </c>
       <c r="G18">
         <v>29.6</v>
@@ -2891,45 +2891,45 @@
         <v>25.9</v>
       </c>
       <c r="M18">
-        <v>8.582220800000002</v>
+        <v>10.2282064</v>
       </c>
       <c r="N18">
-        <v>17.3177792</v>
+        <v>15.6717936</v>
       </c>
       <c r="O18">
-        <v>3.46355584</v>
+        <v>3.134358719999999</v>
       </c>
       <c r="P18">
-        <v>13.85422336</v>
+        <v>12.53743488</v>
       </c>
       <c r="Q18">
-        <v>19.25422336</v>
+        <v>17.93743488</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1017990977149818</v>
+        <v>0.1023566910408305</v>
       </c>
       <c r="T18">
-        <v>0.8662882318035433</v>
+        <v>0.8749140232184944</v>
       </c>
       <c r="U18">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V18">
         <v>0.2</v>
       </c>
       <c r="W18">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.017866890583844</v>
+        <v>2.532213272504942</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09473445356388929</v>
+        <v>0.09531606504719388</v>
       </c>
       <c r="C19">
-        <v>689.3475671137296</v>
+        <v>671.5593015122525</v>
       </c>
       <c r="D19">
-        <v>802.0035671137297</v>
+        <v>792.5833015122525</v>
       </c>
       <c r="E19">
-        <v>127.056</v>
+        <v>135.424</v>
       </c>
       <c r="F19">
-        <v>142.256</v>
+        <v>150.624</v>
       </c>
       <c r="G19">
         <v>29.6</v>
@@ -2973,45 +2973,45 @@
         <v>25.9</v>
       </c>
       <c r="M19">
-        <v>10.2282064</v>
+        <v>11.4172992</v>
       </c>
       <c r="N19">
-        <v>15.6717936</v>
+        <v>14.4827008</v>
       </c>
       <c r="O19">
-        <v>3.134358719999999</v>
+        <v>2.896540159999999</v>
       </c>
       <c r="P19">
-        <v>12.53743488</v>
+        <v>11.58616064</v>
       </c>
       <c r="Q19">
-        <v>17.93743488</v>
+        <v>16.98616064</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1023566910408305</v>
+        <v>0.102927884203895</v>
       </c>
       <c r="T19">
-        <v>0.8749140232184944</v>
+        <v>0.883750199789908</v>
       </c>
       <c r="U19">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.532213272504942</v>
+        <v>2.268487454546167</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09531606504719388</v>
+        <v>0.09536727653049848</v>
       </c>
       <c r="C20">
-        <v>671.5593015122525</v>
+        <v>662.3724272598427</v>
       </c>
       <c r="D20">
-        <v>792.5833015122525</v>
+        <v>791.7644272598427</v>
       </c>
       <c r="E20">
-        <v>135.424</v>
+        <v>143.792</v>
       </c>
       <c r="F20">
-        <v>150.624</v>
+        <v>158.992</v>
       </c>
       <c r="G20">
         <v>29.6</v>
@@ -3055,28 +3055,28 @@
         <v>25.9</v>
       </c>
       <c r="M20">
-        <v>11.4172992</v>
+        <v>12.0515936</v>
       </c>
       <c r="N20">
-        <v>14.4827008</v>
+        <v>13.8484064</v>
       </c>
       <c r="O20">
-        <v>2.89654016</v>
+        <v>2.769681279999999</v>
       </c>
       <c r="P20">
-        <v>11.58616064</v>
+        <v>11.07872512</v>
       </c>
       <c r="Q20">
-        <v>16.98616064</v>
+        <v>16.47872512</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.102927884203895</v>
+        <v>0.10351318090185</v>
       </c>
       <c r="T20">
-        <v>0.8837501997899078</v>
+        <v>0.8928045535606155</v>
       </c>
       <c r="U20">
         <v>0.07580000000000001</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.268487454546168</v>
+        <v>2.149093377991106</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09536727653049848</v>
+        <v>0.09541848801380304</v>
       </c>
       <c r="C21">
-        <v>662.3724272598427</v>
+        <v>653.1872433356474</v>
       </c>
       <c r="D21">
-        <v>791.7644272598427</v>
+        <v>790.9472433356474</v>
       </c>
       <c r="E21">
-        <v>143.792</v>
+        <v>152.16</v>
       </c>
       <c r="F21">
-        <v>158.992</v>
+        <v>167.36</v>
       </c>
       <c r="G21">
         <v>29.6</v>
@@ -3137,28 +3137,28 @@
         <v>25.9</v>
       </c>
       <c r="M21">
-        <v>12.0515936</v>
+        <v>12.685888</v>
       </c>
       <c r="N21">
-        <v>13.8484064</v>
+        <v>13.214112</v>
       </c>
       <c r="O21">
-        <v>2.769681279999999</v>
+        <v>2.6428224</v>
       </c>
       <c r="P21">
-        <v>11.07872512</v>
+        <v>10.5712896</v>
       </c>
       <c r="Q21">
-        <v>16.47872512</v>
+        <v>15.9712896</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.10351318090185</v>
+        <v>0.1041131100172538</v>
       </c>
       <c r="T21">
-        <v>0.8928045535606155</v>
+        <v>0.9020852661755905</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.149093377991106</v>
+        <v>2.041638709091551</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09541848801380304</v>
+        <v>0.0978552994971076</v>
       </c>
       <c r="C22">
-        <v>653.1872433356474</v>
+        <v>607.7934391645372</v>
       </c>
       <c r="D22">
-        <v>790.9472433356474</v>
+        <v>753.9214391645372</v>
       </c>
       <c r="E22">
-        <v>152.16</v>
+        <v>160.528</v>
       </c>
       <c r="F22">
-        <v>167.36</v>
+        <v>175.728</v>
       </c>
       <c r="G22">
         <v>29.6</v>
@@ -3219,45 +3219,45 @@
         <v>25.9</v>
       </c>
       <c r="M22">
-        <v>12.685888</v>
+        <v>15.81552</v>
       </c>
       <c r="N22">
-        <v>13.214112</v>
+        <v>10.08448</v>
       </c>
       <c r="O22">
-        <v>2.6428224</v>
+        <v>2.016895999999999</v>
       </c>
       <c r="P22">
-        <v>10.5712896</v>
+        <v>8.067583999999997</v>
       </c>
       <c r="Q22">
-        <v>15.9712896</v>
+        <v>13.467584</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1041131100172538</v>
+        <v>0.1047282272115286</v>
       </c>
       <c r="T22">
-        <v>0.9020852661755905</v>
+        <v>0.911600933540312</v>
       </c>
       <c r="U22">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.041638709091551</v>
+        <v>1.63763189575809</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0978552994971076</v>
+        <v>0.09802011098041219</v>
       </c>
       <c r="C23">
-        <v>607.7934391645372</v>
+        <v>597.0459936147098</v>
       </c>
       <c r="D23">
-        <v>753.9214391645372</v>
+        <v>751.5419936147098</v>
       </c>
       <c r="E23">
-        <v>160.528</v>
+        <v>168.896</v>
       </c>
       <c r="F23">
-        <v>175.728</v>
+        <v>184.096</v>
       </c>
       <c r="G23">
         <v>29.6</v>
@@ -3301,28 +3301,28 @@
         <v>25.9</v>
       </c>
       <c r="M23">
-        <v>15.81552</v>
+        <v>16.56864</v>
       </c>
       <c r="N23">
-        <v>10.08448</v>
+        <v>9.33136</v>
       </c>
       <c r="O23">
-        <v>2.016896</v>
+        <v>1.866272</v>
       </c>
       <c r="P23">
-        <v>8.067584</v>
+        <v>7.465088</v>
       </c>
       <c r="Q23">
-        <v>13.467584</v>
+        <v>12.865088</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1047282272115286</v>
+        <v>0.1053591166415541</v>
       </c>
       <c r="T23">
-        <v>0.911600933540312</v>
+        <v>0.9213605923759237</v>
       </c>
       <c r="U23">
         <v>0.09</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.637631895758091</v>
+        <v>1.563194082314541</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09802011098041219</v>
+        <v>0.1093848916751309</v>
       </c>
       <c r="C24">
-        <v>597.0459936147098</v>
+        <v>454.3519026945386</v>
       </c>
       <c r="D24">
-        <v>751.5419936147098</v>
+        <v>617.2159026945386</v>
       </c>
       <c r="E24">
-        <v>168.896</v>
+        <v>177.264</v>
       </c>
       <c r="F24">
-        <v>184.096</v>
+        <v>192.464</v>
       </c>
       <c r="G24">
         <v>29.6</v>
@@ -3383,45 +3383,45 @@
         <v>25.9</v>
       </c>
       <c r="M24">
-        <v>16.56864</v>
+        <v>28.25371520000001</v>
       </c>
       <c r="N24">
-        <v>9.33136</v>
+        <v>-2.353715200000007</v>
       </c>
       <c r="O24">
-        <v>1.866272</v>
+        <v>-0.4707430400000014</v>
       </c>
       <c r="P24">
-        <v>7.465088</v>
+        <v>-1.882972160000006</v>
       </c>
       <c r="Q24">
-        <v>12.865088</v>
+        <v>3.517027839999996</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1053591166415541</v>
+        <v>0.1062482340793461</v>
       </c>
       <c r="T24">
-        <v>0.9213605923759237</v>
+        <v>0.9351149563653361</v>
       </c>
       <c r="U24">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V24">
-        <v>0.2</v>
+        <v>0.1833387207074275</v>
       </c>
       <c r="W24">
-        <v>0.07199999999999999</v>
+        <v>0.1198858758001497</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y24">
-        <v>1.563194082314541</v>
+        <v>0.9166936035371375</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1093848916751309</v>
+        <v>0.1103948916751309</v>
       </c>
       <c r="C25">
-        <v>454.3519026945386</v>
+        <v>436.3331695551952</v>
       </c>
       <c r="D25">
-        <v>617.2159026945386</v>
+        <v>607.5651695551952</v>
       </c>
       <c r="E25">
-        <v>177.264</v>
+        <v>185.632</v>
       </c>
       <c r="F25">
-        <v>192.464</v>
+        <v>200.832</v>
       </c>
       <c r="G25">
         <v>29.6</v>
@@ -3465,37 +3465,37 @@
         <v>25.9</v>
       </c>
       <c r="M25">
-        <v>28.25371520000001</v>
+        <v>29.48213760000001</v>
       </c>
       <c r="N25">
-        <v>-2.353715200000007</v>
+        <v>-3.582137600000006</v>
       </c>
       <c r="O25">
-        <v>-0.4707430400000014</v>
+        <v>-0.7164275200000013</v>
       </c>
       <c r="P25">
-        <v>-1.882972160000006</v>
+        <v>-2.865710080000005</v>
       </c>
       <c r="Q25">
-        <v>3.517027839999996</v>
+        <v>2.534289919999997</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1062482340793461</v>
+        <v>0.1070436055803901</v>
       </c>
       <c r="T25">
-        <v>0.9351149563653361</v>
+        <v>0.947419100528038</v>
       </c>
       <c r="U25">
         <v>0.1468</v>
       </c>
       <c r="V25">
-        <v>0.1833387207074275</v>
+        <v>0.175699607344618</v>
       </c>
       <c r="W25">
-        <v>0.1198858758001497</v>
+        <v>0.1210072976418101</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.9166936035371375</v>
+        <v>0.87849803672309</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1103948916751309</v>
+        <v>0.1114048916751309</v>
       </c>
       <c r="C26">
-        <v>436.3331695551952</v>
+        <v>418.6115862234911</v>
       </c>
       <c r="D26">
-        <v>607.5651695551952</v>
+        <v>598.2115862234912</v>
       </c>
       <c r="E26">
-        <v>185.632</v>
+        <v>194</v>
       </c>
       <c r="F26">
-        <v>200.832</v>
+        <v>209.2</v>
       </c>
       <c r="G26">
         <v>29.6</v>
@@ -3547,37 +3547,37 @@
         <v>25.9</v>
       </c>
       <c r="M26">
-        <v>29.48213760000001</v>
+        <v>30.71056</v>
       </c>
       <c r="N26">
-        <v>-3.582137600000006</v>
+        <v>-4.810560000000006</v>
       </c>
       <c r="O26">
-        <v>-0.7164275200000013</v>
+        <v>-0.9621120000000012</v>
       </c>
       <c r="P26">
-        <v>-2.865710080000005</v>
+        <v>-3.848448000000005</v>
       </c>
       <c r="Q26">
-        <v>2.534289919999997</v>
+        <v>1.551551999999997</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1070436055803901</v>
+        <v>0.1078601869881287</v>
       </c>
       <c r="T26">
-        <v>0.9474191005280379</v>
+        <v>0.9600513552017451</v>
       </c>
       <c r="U26">
         <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.175699607344618</v>
+        <v>0.1686716230508333</v>
       </c>
       <c r="W26">
-        <v>0.1210072976418101</v>
+        <v>0.1220390057361377</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.87849803672309</v>
+        <v>0.8433581152541665</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1114048916751309</v>
+        <v>0.1124148916751309</v>
       </c>
       <c r="C27">
-        <v>418.6115862234911</v>
+        <v>401.1736367438424</v>
       </c>
       <c r="D27">
-        <v>598.2115862234912</v>
+        <v>589.1416367438424</v>
       </c>
       <c r="E27">
-        <v>194</v>
+        <v>202.368</v>
       </c>
       <c r="F27">
-        <v>209.2</v>
+        <v>217.568</v>
       </c>
       <c r="G27">
         <v>29.6</v>
@@ -3629,37 +3629,37 @@
         <v>25.9</v>
       </c>
       <c r="M27">
-        <v>30.71056</v>
+        <v>31.9389824</v>
       </c>
       <c r="N27">
-        <v>-4.810560000000006</v>
+        <v>-6.038982400000005</v>
       </c>
       <c r="O27">
-        <v>-0.9621120000000012</v>
+        <v>-1.207796480000001</v>
       </c>
       <c r="P27">
-        <v>-3.848448000000005</v>
+        <v>-4.831185920000005</v>
       </c>
       <c r="Q27">
-        <v>1.551551999999997</v>
+        <v>0.5688140799999974</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1078601869881287</v>
+        <v>0.1086988381636439</v>
       </c>
       <c r="T27">
-        <v>0.9600513552017451</v>
+        <v>0.9730250221639308</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.1686716230508333</v>
+        <v>0.1621842529334936</v>
       </c>
       <c r="W27">
-        <v>0.1220390057361377</v>
+        <v>0.1229913516693631</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8433581152541665</v>
+        <v>0.8109212646674677</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1124148916751309</v>
+        <v>0.1285559493332843</v>
       </c>
       <c r="C28">
-        <v>401.1736367438424</v>
+        <v>277.8970506649851</v>
       </c>
       <c r="D28">
-        <v>589.1416367438424</v>
+        <v>474.2330506649851</v>
       </c>
       <c r="E28">
-        <v>202.368</v>
+        <v>210.736</v>
       </c>
       <c r="F28">
-        <v>217.568</v>
+        <v>225.936</v>
       </c>
       <c r="G28">
         <v>29.6</v>
@@ -3711,45 +3711,45 @@
         <v>25.9</v>
       </c>
       <c r="M28">
-        <v>31.9389824</v>
+        <v>45.36794880000001</v>
       </c>
       <c r="N28">
-        <v>-6.038982400000005</v>
+        <v>-19.46794880000001</v>
       </c>
       <c r="O28">
-        <v>-1.207796480000001</v>
+        <v>-3.893589760000002</v>
       </c>
       <c r="P28">
-        <v>-4.831185920000005</v>
+        <v>-15.57435904000001</v>
       </c>
       <c r="Q28">
-        <v>0.5688140799999974</v>
+        <v>-10.17435904000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1086988381636439</v>
+        <v>0.1103153395880136</v>
       </c>
       <c r="T28">
-        <v>0.9730250221639308</v>
+        <v>0.9980317850898716</v>
       </c>
       <c r="U28">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.1621842529334936</v>
+        <v>0.1141775226126159</v>
       </c>
       <c r="W28">
-        <v>0.1229913516693631</v>
+        <v>0.1778731534593868</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.8109212646674677</v>
+        <v>0.5708876130630793</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1285559493332843</v>
+        <v>0.1301059493332843</v>
       </c>
       <c r="C29">
-        <v>277.8970506649851</v>
+        <v>260.8100784649944</v>
       </c>
       <c r="D29">
-        <v>474.2330506649851</v>
+        <v>465.5140784649944</v>
       </c>
       <c r="E29">
-        <v>210.736</v>
+        <v>219.104</v>
       </c>
       <c r="F29">
-        <v>225.936</v>
+        <v>234.304</v>
       </c>
       <c r="G29">
         <v>29.6</v>
@@ -3793,37 +3793,37 @@
         <v>25.9</v>
       </c>
       <c r="M29">
-        <v>45.36794880000001</v>
+        <v>47.04824320000001</v>
       </c>
       <c r="N29">
-        <v>-19.46794880000001</v>
+        <v>-21.14824320000001</v>
       </c>
       <c r="O29">
-        <v>-3.893589760000002</v>
+        <v>-4.229648640000002</v>
       </c>
       <c r="P29">
-        <v>-15.57435904000001</v>
+        <v>-16.91859456000001</v>
       </c>
       <c r="Q29">
-        <v>-10.17435904000001</v>
+        <v>-11.51859456000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1103153395880136</v>
+        <v>0.1112113859711804</v>
       </c>
       <c r="T29">
-        <v>0.9980317850898716</v>
+        <v>1.011893337660564</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.1141775226126159</v>
+        <v>0.1100997539478796</v>
       </c>
       <c r="W29">
-        <v>0.1778731534593868</v>
+        <v>0.1786919694072658</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.5708876130630793</v>
+        <v>0.5504987697393979</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1301059493332843</v>
+        <v>0.1316559493332843</v>
       </c>
       <c r="C30">
-        <v>260.8100784649944</v>
+        <v>244.0379221167864</v>
       </c>
       <c r="D30">
-        <v>465.5140784649944</v>
+        <v>457.1099221167864</v>
       </c>
       <c r="E30">
-        <v>219.104</v>
+        <v>227.4720000000001</v>
       </c>
       <c r="F30">
-        <v>234.304</v>
+        <v>242.6720000000001</v>
       </c>
       <c r="G30">
         <v>29.6</v>
@@ -3875,37 +3875,37 @@
         <v>25.9</v>
       </c>
       <c r="M30">
-        <v>47.04824320000001</v>
+        <v>48.72853760000001</v>
       </c>
       <c r="N30">
-        <v>-21.14824320000001</v>
+        <v>-22.82853760000001</v>
       </c>
       <c r="O30">
-        <v>-4.229648640000002</v>
+        <v>-4.565707520000003</v>
       </c>
       <c r="P30">
-        <v>-16.91859456000001</v>
+        <v>-18.26283008000001</v>
       </c>
       <c r="Q30">
-        <v>-11.51859456000001</v>
+        <v>-12.86283008000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1112113859711804</v>
+        <v>0.1121326730975351</v>
       </c>
       <c r="T30">
-        <v>1.011893337660564</v>
+        <v>1.026145356500854</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.1100997539478796</v>
+        <v>0.1063032107082975</v>
       </c>
       <c r="W30">
-        <v>0.1786919694072658</v>
+        <v>0.1794543152897739</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5504987697393979</v>
+        <v>0.5315160535414876</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1316559493332843</v>
+        <v>0.1332059493332843</v>
       </c>
       <c r="C31">
-        <v>244.0379221167865</v>
+        <v>227.5638334044565</v>
       </c>
       <c r="D31">
-        <v>457.1099221167864</v>
+        <v>449.0038334044565</v>
       </c>
       <c r="E31">
-        <v>227.472</v>
+        <v>235.84</v>
       </c>
       <c r="F31">
-        <v>242.672</v>
+        <v>251.04</v>
       </c>
       <c r="G31">
         <v>29.6</v>
@@ -3957,37 +3957,37 @@
         <v>25.9</v>
       </c>
       <c r="M31">
-        <v>48.7285376</v>
+        <v>50.408832</v>
       </c>
       <c r="N31">
-        <v>-22.8285376</v>
+        <v>-24.50883200000001</v>
       </c>
       <c r="O31">
-        <v>-4.565707520000001</v>
+        <v>-4.901766400000001</v>
       </c>
       <c r="P31">
-        <v>-18.26283008</v>
+        <v>-19.60706560000001</v>
       </c>
       <c r="Q31">
-        <v>-12.86283008</v>
+        <v>-14.2070656</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1121326730975351</v>
+        <v>0.1130802827132142</v>
       </c>
       <c r="T31">
-        <v>1.026145356500854</v>
+        <v>1.040804575879438</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.1063032107082975</v>
+        <v>0.1027597703513543</v>
       </c>
       <c r="W31">
-        <v>0.1794543152897739</v>
+        <v>0.1801658381134481</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5315160535414878</v>
+        <v>0.5137988517567714</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1332059493332843</v>
+        <v>0.1458283077543876</v>
       </c>
       <c r="C32">
-        <v>227.5638334044565</v>
+        <v>162.5369990713146</v>
       </c>
       <c r="D32">
-        <v>449.0038334044565</v>
+        <v>392.3449990713146</v>
       </c>
       <c r="E32">
-        <v>235.84</v>
+        <v>244.208</v>
       </c>
       <c r="F32">
-        <v>251.04</v>
+        <v>259.408</v>
       </c>
       <c r="G32">
         <v>29.6</v>
@@ -4039,45 +4039,45 @@
         <v>25.9</v>
       </c>
       <c r="M32">
-        <v>50.408832</v>
+        <v>61.16840640000001</v>
       </c>
       <c r="N32">
-        <v>-24.50883200000001</v>
+        <v>-35.26840640000001</v>
       </c>
       <c r="O32">
-        <v>-4.901766400000001</v>
+        <v>-7.053681280000003</v>
       </c>
       <c r="P32">
-        <v>-19.60706560000001</v>
+        <v>-28.21472512000001</v>
       </c>
       <c r="Q32">
-        <v>-14.2070656</v>
+        <v>-22.81472512000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1130802827132142</v>
+        <v>0.1143776178555844</v>
       </c>
       <c r="T32">
-        <v>1.040804575879438</v>
+        <v>1.060873937929887</v>
       </c>
       <c r="U32">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.1027597703513543</v>
+        <v>0.08468423986929303</v>
       </c>
       <c r="W32">
-        <v>0.1801658381134481</v>
+        <v>0.2158314562388207</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.5137988517567714</v>
+        <v>0.4234211993464652</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1458283077543876</v>
+        <v>0.1477283077543876</v>
       </c>
       <c r="C33">
-        <v>162.5369990713146</v>
+        <v>146.8554714099726</v>
       </c>
       <c r="D33">
-        <v>392.3449990713146</v>
+        <v>385.0314714099725</v>
       </c>
       <c r="E33">
-        <v>244.208</v>
+        <v>252.576</v>
       </c>
       <c r="F33">
-        <v>259.408</v>
+        <v>267.776</v>
       </c>
       <c r="G33">
         <v>29.6</v>
@@ -4121,37 +4121,37 @@
         <v>25.9</v>
       </c>
       <c r="M33">
-        <v>61.16840640000001</v>
+        <v>63.14158080000001</v>
       </c>
       <c r="N33">
-        <v>-35.26840640000001</v>
+        <v>-37.24158080000001</v>
       </c>
       <c r="O33">
-        <v>-7.053681280000003</v>
+        <v>-7.448316160000002</v>
       </c>
       <c r="P33">
-        <v>-28.21472512000001</v>
+        <v>-29.79326464000001</v>
       </c>
       <c r="Q33">
-        <v>-22.81472512000001</v>
+        <v>-24.39326464000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1143776178555844</v>
+        <v>0.1153861122358135</v>
       </c>
       <c r="T33">
-        <v>1.060873937929887</v>
+        <v>1.076475025252385</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.08468423986929303</v>
+        <v>0.08203785737337763</v>
       </c>
       <c r="W33">
-        <v>0.2158314562388207</v>
+        <v>0.2164554732313576</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.4234211993464652</v>
+        <v>0.4101892868668882</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1477283077543876</v>
+        <v>0.1496283077543876</v>
       </c>
       <c r="C34">
-        <v>146.8554714099726</v>
+        <v>131.4416106856553</v>
       </c>
       <c r="D34">
-        <v>385.0314714099725</v>
+        <v>377.9856106856553</v>
       </c>
       <c r="E34">
-        <v>252.576</v>
+        <v>260.9440000000001</v>
       </c>
       <c r="F34">
-        <v>267.776</v>
+        <v>276.1440000000001</v>
       </c>
       <c r="G34">
         <v>29.6</v>
@@ -4203,37 +4203,37 @@
         <v>25.9</v>
       </c>
       <c r="M34">
-        <v>63.14158080000001</v>
+        <v>65.11475520000002</v>
       </c>
       <c r="N34">
-        <v>-37.24158080000001</v>
+        <v>-39.21475520000002</v>
       </c>
       <c r="O34">
-        <v>-7.448316160000002</v>
+        <v>-7.842951040000004</v>
       </c>
       <c r="P34">
-        <v>-29.79326464000001</v>
+        <v>-31.37180416000002</v>
       </c>
       <c r="Q34">
-        <v>-24.39326464000001</v>
+        <v>-25.97180416000002</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1153861122358135</v>
+        <v>0.1164247109259003</v>
       </c>
       <c r="T34">
-        <v>1.076475025252385</v>
+        <v>1.092541816674063</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.08203785737337763</v>
+        <v>0.07955186169539648</v>
       </c>
       <c r="W34">
-        <v>0.2164554732313576</v>
+        <v>0.2170416710122255</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.4101892868668882</v>
+        <v>0.3977593084769824</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1496283077543876</v>
+        <v>0.1515283077543876</v>
       </c>
       <c r="C35">
-        <v>131.4416106856553</v>
+        <v>116.2809865005497</v>
       </c>
       <c r="D35">
-        <v>377.9856106856553</v>
+        <v>371.1929865005497</v>
       </c>
       <c r="E35">
-        <v>260.9440000000001</v>
+        <v>269.3120000000001</v>
       </c>
       <c r="F35">
-        <v>276.1440000000001</v>
+        <v>284.5120000000001</v>
       </c>
       <c r="G35">
         <v>29.6</v>
@@ -4285,37 +4285,37 @@
         <v>25.9</v>
       </c>
       <c r="M35">
-        <v>65.11475520000002</v>
+        <v>67.08792960000001</v>
       </c>
       <c r="N35">
-        <v>-39.21475520000002</v>
+        <v>-41.18792960000001</v>
       </c>
       <c r="O35">
-        <v>-7.842951040000004</v>
+        <v>-8.237585920000003</v>
       </c>
       <c r="P35">
-        <v>-31.37180416000002</v>
+        <v>-32.95034368000001</v>
       </c>
       <c r="Q35">
-        <v>-25.97180416000002</v>
+        <v>-27.55034368000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1164247109259003</v>
+        <v>0.1174947823035655</v>
       </c>
       <c r="T35">
-        <v>1.092541816674063</v>
+        <v>1.109095480563064</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.07955186169539648</v>
+        <v>0.07721210105729659</v>
       </c>
       <c r="W35">
-        <v>0.2170416710122255</v>
+        <v>0.2175933865706895</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3977593084769824</v>
+        <v>0.3860605052864829</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1515283077543876</v>
+        <v>0.1534283077543876</v>
       </c>
       <c r="C36">
-        <v>116.2809865005497</v>
+        <v>101.3601874361948</v>
       </c>
       <c r="D36">
-        <v>371.1929865005497</v>
+        <v>364.6401874361948</v>
       </c>
       <c r="E36">
-        <v>269.3120000000001</v>
+        <v>277.6800000000001</v>
       </c>
       <c r="F36">
-        <v>284.5120000000001</v>
+        <v>292.8800000000001</v>
       </c>
       <c r="G36">
         <v>29.6</v>
@@ -4367,37 +4367,37 @@
         <v>25.9</v>
       </c>
       <c r="M36">
-        <v>67.08792960000001</v>
+        <v>69.06110400000001</v>
       </c>
       <c r="N36">
-        <v>-41.18792960000001</v>
+        <v>-43.16110400000002</v>
       </c>
       <c r="O36">
-        <v>-8.237585920000003</v>
+        <v>-8.632220800000004</v>
       </c>
       <c r="P36">
-        <v>-32.95034368000001</v>
+        <v>-34.52888320000001</v>
       </c>
       <c r="Q36">
-        <v>-27.55034368000001</v>
+        <v>-29.12888320000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1174947823035655</v>
+        <v>0.1185977789543896</v>
       </c>
       <c r="T36">
-        <v>1.109095480563064</v>
+        <v>1.126158487956341</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.07721210105729659</v>
+        <v>0.07500604102708812</v>
       </c>
       <c r="W36">
-        <v>0.2175933865706895</v>
+        <v>0.2181135755258126</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3860605052864829</v>
+        <v>0.3750302051354405</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1534283077543876</v>
+        <v>0.1553283077543876</v>
       </c>
       <c r="C37">
-        <v>101.3601874361948</v>
+        <v>86.6667326717299</v>
       </c>
       <c r="D37">
-        <v>364.6401874361948</v>
+        <v>358.3147326717299</v>
       </c>
       <c r="E37">
-        <v>277.6800000000001</v>
+        <v>286.0480000000001</v>
       </c>
       <c r="F37">
-        <v>292.8800000000001</v>
+        <v>301.248</v>
       </c>
       <c r="G37">
         <v>29.6</v>
@@ -4449,37 +4449,37 @@
         <v>25.9</v>
       </c>
       <c r="M37">
-        <v>69.06110400000001</v>
+        <v>71.03427840000002</v>
       </c>
       <c r="N37">
-        <v>-43.16110400000002</v>
+        <v>-45.13427840000002</v>
       </c>
       <c r="O37">
-        <v>-8.632220800000004</v>
+        <v>-9.026855680000004</v>
       </c>
       <c r="P37">
-        <v>-34.52888320000001</v>
+        <v>-36.10742272000002</v>
       </c>
       <c r="Q37">
-        <v>-29.12888320000001</v>
+        <v>-30.70742272000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1185977789543896</v>
+        <v>0.1197352442505519</v>
       </c>
       <c r="T37">
-        <v>1.126158487956341</v>
+        <v>1.143754714330659</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.07500604102708812</v>
+        <v>0.07292253988744678</v>
       </c>
       <c r="W37">
-        <v>0.2181135755258126</v>
+        <v>0.2186048650945401</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3750302051354405</v>
+        <v>0.3646126994372338</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1553283077543876</v>
+        <v>0.1572283077543876</v>
       </c>
       <c r="C38">
-        <v>86.66673267172996</v>
+        <v>72.18899264429524</v>
       </c>
       <c r="D38">
-        <v>358.3147326717299</v>
+        <v>352.2049926442953</v>
       </c>
       <c r="E38">
-        <v>286.048</v>
+        <v>294.4160000000001</v>
       </c>
       <c r="F38">
-        <v>301.248</v>
+        <v>309.616</v>
       </c>
       <c r="G38">
         <v>29.6</v>
@@ -4531,37 +4531,37 @@
         <v>25.9</v>
       </c>
       <c r="M38">
-        <v>71.03427840000001</v>
+        <v>73.00745280000001</v>
       </c>
       <c r="N38">
-        <v>-45.13427840000001</v>
+        <v>-47.10745280000001</v>
       </c>
       <c r="O38">
-        <v>-9.026855680000002</v>
+        <v>-9.421490560000002</v>
       </c>
       <c r="P38">
-        <v>-36.10742272</v>
+        <v>-37.68596224000001</v>
       </c>
       <c r="Q38">
-        <v>-30.70742272</v>
+        <v>-32.28596224</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1197352442505519</v>
+        <v>0.1209088195561162</v>
       </c>
       <c r="T38">
-        <v>1.143754714330659</v>
+        <v>1.161909551066066</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07292253988744678</v>
+        <v>0.0709516604310293</v>
       </c>
       <c r="W38">
-        <v>0.2186048650945401</v>
+        <v>0.2190695984703633</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.364612699437234</v>
+        <v>0.3547583021551465</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1572283077543876</v>
+        <v>0.1591283077543876</v>
       </c>
       <c r="C39">
-        <v>72.18899264429524</v>
+        <v>57.91611769041816</v>
       </c>
       <c r="D39">
-        <v>352.2049926442953</v>
+        <v>346.3001176904182</v>
       </c>
       <c r="E39">
-        <v>294.4160000000001</v>
+        <v>302.784</v>
       </c>
       <c r="F39">
-        <v>309.616</v>
+        <v>317.984</v>
       </c>
       <c r="G39">
         <v>29.6</v>
@@ -4613,37 +4613,37 @@
         <v>25.9</v>
       </c>
       <c r="M39">
-        <v>73.00745280000001</v>
+        <v>74.98062720000001</v>
       </c>
       <c r="N39">
-        <v>-47.10745280000001</v>
+        <v>-49.08062720000002</v>
       </c>
       <c r="O39">
-        <v>-9.421490560000002</v>
+        <v>-9.816125440000004</v>
       </c>
       <c r="P39">
-        <v>-37.68596224000001</v>
+        <v>-39.26450176000002</v>
       </c>
       <c r="Q39">
-        <v>-32.28596224</v>
+        <v>-33.86450176000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1209088195561162</v>
+        <v>0.122120252129602</v>
       </c>
       <c r="T39">
-        <v>1.161909551066066</v>
+        <v>1.180650027696164</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.0709516604310293</v>
+        <v>0.06908451147231801</v>
       </c>
       <c r="W39">
-        <v>0.2190695984703633</v>
+        <v>0.2195098721948274</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3547583021551465</v>
+        <v>0.34542255736159</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1591283077543876</v>
+        <v>0.1610283077543876</v>
       </c>
       <c r="C40">
-        <v>57.91611769041816</v>
+        <v>43.83797374719302</v>
       </c>
       <c r="D40">
-        <v>346.3001176904182</v>
+        <v>340.589973747193</v>
       </c>
       <c r="E40">
-        <v>302.784</v>
+        <v>311.152</v>
       </c>
       <c r="F40">
-        <v>317.984</v>
+        <v>326.352</v>
       </c>
       <c r="G40">
         <v>29.6</v>
@@ -4695,37 +4695,37 @@
         <v>25.9</v>
       </c>
       <c r="M40">
-        <v>74.98062720000001</v>
+        <v>76.95380160000001</v>
       </c>
       <c r="N40">
-        <v>-49.08062720000002</v>
+        <v>-51.05380160000001</v>
       </c>
       <c r="O40">
-        <v>-9.816125440000004</v>
+        <v>-10.21076032</v>
       </c>
       <c r="P40">
-        <v>-39.26450176000002</v>
+        <v>-40.84304128000001</v>
       </c>
       <c r="Q40">
-        <v>-33.86450176000001</v>
+        <v>-35.44304128</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.122120252129602</v>
+        <v>0.1233714038038577</v>
       </c>
       <c r="T40">
-        <v>1.180650027696164</v>
+        <v>1.200004946182987</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06908451147231801</v>
+        <v>0.06731311374225857</v>
       </c>
       <c r="W40">
-        <v>0.2195098721948274</v>
+        <v>0.2199275677795755</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.34542255736159</v>
+        <v>0.3365655687112928</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1610283077543876</v>
+        <v>0.1629283077543876</v>
       </c>
       <c r="C41">
-        <v>43.83797374719302</v>
+        <v>29.94508431161233</v>
       </c>
       <c r="D41">
-        <v>340.589973747193</v>
+        <v>335.0650843116123</v>
       </c>
       <c r="E41">
-        <v>311.152</v>
+        <v>319.52</v>
       </c>
       <c r="F41">
-        <v>326.352</v>
+        <v>334.72</v>
       </c>
       <c r="G41">
         <v>29.6</v>
@@ -4777,37 +4777,37 @@
         <v>25.9</v>
       </c>
       <c r="M41">
-        <v>76.95380160000001</v>
+        <v>78.92697600000001</v>
       </c>
       <c r="N41">
-        <v>-51.05380160000001</v>
+        <v>-53.02697600000001</v>
       </c>
       <c r="O41">
-        <v>-10.21076032</v>
+        <v>-10.6053952</v>
       </c>
       <c r="P41">
-        <v>-40.84304128000001</v>
+        <v>-42.42158080000001</v>
       </c>
       <c r="Q41">
-        <v>-35.44304128</v>
+        <v>-37.02158080000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1233714038038577</v>
+        <v>0.124664260533922</v>
       </c>
       <c r="T41">
-        <v>1.200004946182987</v>
+        <v>1.22000502861937</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06731311374225857</v>
+        <v>0.06563028589870211</v>
       </c>
       <c r="W41">
-        <v>0.2199275677795755</v>
+        <v>0.2203243785850861</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3365655687112928</v>
+        <v>0.3281514294935105</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1629283077543876</v>
+        <v>0.1648283077543876</v>
       </c>
       <c r="C42">
-        <v>29.94508431161233</v>
+        <v>16.22857795877297</v>
       </c>
       <c r="D42">
-        <v>335.0650843116123</v>
+        <v>329.716577958773</v>
       </c>
       <c r="E42">
-        <v>319.52</v>
+        <v>327.8880000000001</v>
       </c>
       <c r="F42">
-        <v>334.72</v>
+        <v>343.0880000000001</v>
       </c>
       <c r="G42">
         <v>29.6</v>
@@ -4859,37 +4859,37 @@
         <v>25.9</v>
       </c>
       <c r="M42">
-        <v>78.92697600000001</v>
+        <v>80.90015040000002</v>
       </c>
       <c r="N42">
-        <v>-53.02697600000001</v>
+        <v>-55.00015040000002</v>
       </c>
       <c r="O42">
-        <v>-10.6053952</v>
+        <v>-11.00003008</v>
       </c>
       <c r="P42">
-        <v>-42.42158080000001</v>
+        <v>-44.00012032000001</v>
       </c>
       <c r="Q42">
-        <v>-37.02158080000001</v>
+        <v>-38.60012032000002</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.124664260533922</v>
+        <v>0.1260009429158529</v>
       </c>
       <c r="T42">
-        <v>1.22000502861937</v>
+        <v>1.240683079951902</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06563028589870211</v>
+        <v>0.06402954721824596</v>
       </c>
       <c r="W42">
-        <v>0.2203243785850861</v>
+        <v>0.2207018327659376</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3281514294935105</v>
+        <v>0.3201477360912297</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1648283077543876</v>
+        <v>0.1667283077543876</v>
       </c>
       <c r="C43">
-        <v>16.22857795877297</v>
+        <v>2.680140807580472</v>
       </c>
       <c r="D43">
-        <v>329.716577958773</v>
+        <v>324.5361408075805</v>
       </c>
       <c r="E43">
-        <v>327.8880000000001</v>
+        <v>336.2560000000001</v>
       </c>
       <c r="F43">
-        <v>343.0880000000001</v>
+        <v>351.4560000000001</v>
       </c>
       <c r="G43">
         <v>29.6</v>
@@ -4941,37 +4941,37 @@
         <v>25.9</v>
       </c>
       <c r="M43">
-        <v>80.90015040000002</v>
+        <v>82.87332480000002</v>
       </c>
       <c r="N43">
-        <v>-55.00015040000002</v>
+        <v>-56.97332480000002</v>
       </c>
       <c r="O43">
-        <v>-11.00003008</v>
+        <v>-11.39466496000001</v>
       </c>
       <c r="P43">
-        <v>-44.00012032000001</v>
+        <v>-45.57865984000001</v>
       </c>
       <c r="Q43">
-        <v>-38.60012032000002</v>
+        <v>-40.17865984000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1260009429158529</v>
+        <v>0.1273837177937124</v>
       </c>
       <c r="T43">
-        <v>1.240683079951902</v>
+        <v>1.262074167537279</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06402954721824596</v>
+        <v>0.06250503418924008</v>
       </c>
       <c r="W43">
-        <v>0.2207018327659376</v>
+        <v>0.2210613129381772</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3201477360912297</v>
+        <v>0.3125251709462005</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1667283077543876</v>
+        <v>0.1686283077543876</v>
       </c>
       <c r="C44">
-        <v>2.680140807580528</v>
+        <v>-10.70802660177128</v>
       </c>
       <c r="D44">
-        <v>324.5361408075805</v>
+        <v>319.5159733982287</v>
       </c>
       <c r="E44">
-        <v>336.256</v>
+        <v>344.624</v>
       </c>
       <c r="F44">
-        <v>351.456</v>
+        <v>359.824</v>
       </c>
       <c r="G44">
         <v>29.6</v>
@@ -5023,37 +5023,37 @@
         <v>25.9</v>
       </c>
       <c r="M44">
-        <v>82.87332480000001</v>
+        <v>84.84649920000001</v>
       </c>
       <c r="N44">
-        <v>-56.97332480000001</v>
+        <v>-58.94649920000001</v>
       </c>
       <c r="O44">
-        <v>-11.39466496</v>
+        <v>-11.78929984</v>
       </c>
       <c r="P44">
-        <v>-45.57865984000001</v>
+        <v>-47.15719936000001</v>
       </c>
       <c r="Q44">
-        <v>-40.17865984000001</v>
+        <v>-41.75719936</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1273837177937124</v>
+        <v>0.128815011088339</v>
       </c>
       <c r="T44">
-        <v>1.262074167537279</v>
+        <v>1.284215819599337</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.0625050341892401</v>
+        <v>0.0610514287429787</v>
       </c>
       <c r="W44">
-        <v>0.2210613129381772</v>
+        <v>0.2214040731024056</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3125251709462005</v>
+        <v>0.3052571437148935</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1686283077543876</v>
+        <v>0.1705283077543877</v>
       </c>
       <c r="C45">
-        <v>-10.70802660177128</v>
+        <v>-23.9432484889798</v>
       </c>
       <c r="D45">
-        <v>319.5159733982287</v>
+        <v>314.6487515110202</v>
       </c>
       <c r="E45">
-        <v>344.624</v>
+        <v>352.992</v>
       </c>
       <c r="F45">
-        <v>359.824</v>
+        <v>368.192</v>
       </c>
       <c r="G45">
         <v>29.6</v>
@@ -5105,37 +5105,37 @@
         <v>25.9</v>
       </c>
       <c r="M45">
-        <v>84.84649920000001</v>
+        <v>86.8196736</v>
       </c>
       <c r="N45">
-        <v>-58.94649920000001</v>
+        <v>-60.9196736</v>
       </c>
       <c r="O45">
-        <v>-11.78929984</v>
+        <v>-12.18393472</v>
       </c>
       <c r="P45">
-        <v>-47.15719936000001</v>
+        <v>-48.73573888</v>
       </c>
       <c r="Q45">
-        <v>-41.75719936</v>
+        <v>-43.33573887999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.128815011088339</v>
+        <v>0.1302974220006307</v>
       </c>
       <c r="T45">
-        <v>1.284215819599337</v>
+        <v>1.307148244949325</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.0610514287429787</v>
+        <v>0.05966389627154737</v>
       </c>
       <c r="W45">
-        <v>0.2214040731024056</v>
+        <v>0.2217312532591691</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3052571437148935</v>
+        <v>0.2983194813577369</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1705283077543877</v>
+        <v>0.1724283077543876</v>
       </c>
       <c r="C46">
-        <v>-23.9432484889798</v>
+        <v>-37.03240948743928</v>
       </c>
       <c r="D46">
-        <v>314.6487515110202</v>
+        <v>309.9275905125608</v>
       </c>
       <c r="E46">
-        <v>352.992</v>
+        <v>361.3600000000001</v>
       </c>
       <c r="F46">
-        <v>368.192</v>
+        <v>376.5600000000001</v>
       </c>
       <c r="G46">
         <v>29.6</v>
@@ -5187,37 +5187,37 @@
         <v>25.9</v>
       </c>
       <c r="M46">
-        <v>86.8196736</v>
+        <v>88.79284800000002</v>
       </c>
       <c r="N46">
-        <v>-60.9196736</v>
+        <v>-62.89284800000002</v>
       </c>
       <c r="O46">
-        <v>-12.18393472</v>
+        <v>-12.57856960000001</v>
       </c>
       <c r="P46">
-        <v>-48.73573888</v>
+        <v>-50.31427840000002</v>
       </c>
       <c r="Q46">
-        <v>-43.33573887999999</v>
+        <v>-44.91427840000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1302974220006307</v>
+        <v>0.1318337387642786</v>
       </c>
       <c r="T46">
-        <v>1.307148244949325</v>
+        <v>1.330914576675676</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05966389627154737</v>
+        <v>0.05833803190995741</v>
       </c>
       <c r="W46">
-        <v>0.2217312532591691</v>
+        <v>0.222043892075632</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2983194813577369</v>
+        <v>0.2916901595497871</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1724283077543876</v>
+        <v>0.1743283077543877</v>
       </c>
       <c r="C47">
-        <v>-37.03240948743928</v>
+        <v>-49.98198713568127</v>
       </c>
       <c r="D47">
-        <v>309.9275905125608</v>
+        <v>305.3460128643188</v>
       </c>
       <c r="E47">
-        <v>361.3600000000001</v>
+        <v>369.7280000000001</v>
       </c>
       <c r="F47">
-        <v>376.5600000000001</v>
+        <v>384.9280000000001</v>
       </c>
       <c r="G47">
         <v>29.6</v>
@@ -5269,37 +5269,37 @@
         <v>25.9</v>
       </c>
       <c r="M47">
-        <v>88.79284800000002</v>
+        <v>90.76602240000001</v>
       </c>
       <c r="N47">
-        <v>-62.89284800000002</v>
+        <v>-64.86602240000002</v>
       </c>
       <c r="O47">
-        <v>-12.57856960000001</v>
+        <v>-12.97320448000001</v>
       </c>
       <c r="P47">
-        <v>-50.31427840000002</v>
+        <v>-51.89281792000001</v>
       </c>
       <c r="Q47">
-        <v>-44.91427840000001</v>
+        <v>-46.49281792000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1318337387642786</v>
+        <v>0.1334269561488022</v>
       </c>
       <c r="T47">
-        <v>1.330914576675676</v>
+        <v>1.355561142910411</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05833803190995741</v>
+        <v>0.05706981382495835</v>
       </c>
       <c r="W47">
-        <v>0.222043892075632</v>
+        <v>0.2223429379000748</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2916901595497871</v>
+        <v>0.2853490691247916</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1743283077543877</v>
+        <v>0.1762283077543876</v>
       </c>
       <c r="C48">
-        <v>-49.98198713568127</v>
+        <v>-62.7980815289223</v>
       </c>
       <c r="D48">
-        <v>305.3460128643188</v>
+        <v>300.8979184710777</v>
       </c>
       <c r="E48">
-        <v>369.7280000000001</v>
+        <v>378.0960000000001</v>
       </c>
       <c r="F48">
-        <v>384.9280000000001</v>
+        <v>393.296</v>
       </c>
       <c r="G48">
         <v>29.6</v>
@@ -5351,37 +5351,37 @@
         <v>25.9</v>
       </c>
       <c r="M48">
-        <v>90.76602240000001</v>
+        <v>92.73919680000002</v>
       </c>
       <c r="N48">
-        <v>-64.86602240000002</v>
+        <v>-66.83919680000002</v>
       </c>
       <c r="O48">
-        <v>-12.97320448000001</v>
+        <v>-13.36783936</v>
       </c>
       <c r="P48">
-        <v>-51.89281792000001</v>
+        <v>-53.47135744000002</v>
       </c>
       <c r="Q48">
-        <v>-46.49281792000001</v>
+        <v>-48.07135744000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1334269561488022</v>
+        <v>0.1350802949440627</v>
       </c>
       <c r="T48">
-        <v>1.355561142910411</v>
+        <v>1.381137768248343</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05706981382495835</v>
+        <v>0.05585556246698051</v>
       </c>
       <c r="W48">
-        <v>0.2223429379000748</v>
+        <v>0.222629258370286</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2853490691247916</v>
+        <v>0.2792778123349025</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1762283077543876</v>
+        <v>0.1781283077543876</v>
       </c>
       <c r="C49">
-        <v>-62.7980815289223</v>
+        <v>-75.48644241614971</v>
       </c>
       <c r="D49">
-        <v>300.8979184710777</v>
+        <v>296.5775575838503</v>
       </c>
       <c r="E49">
-        <v>378.0960000000001</v>
+        <v>386.4640000000001</v>
       </c>
       <c r="F49">
-        <v>393.296</v>
+        <v>401.664</v>
       </c>
       <c r="G49">
         <v>29.6</v>
@@ -5433,37 +5433,37 @@
         <v>25.9</v>
       </c>
       <c r="M49">
-        <v>92.73919680000002</v>
+        <v>94.71237120000002</v>
       </c>
       <c r="N49">
-        <v>-66.83919680000002</v>
+        <v>-68.81237120000003</v>
       </c>
       <c r="O49">
-        <v>-13.36783936</v>
+        <v>-13.76247424000001</v>
       </c>
       <c r="P49">
-        <v>-53.47135744000002</v>
+        <v>-55.04989696000003</v>
       </c>
       <c r="Q49">
-        <v>-48.07135744000001</v>
+        <v>-49.64989696000002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1350802949440627</v>
+        <v>0.1367972236929869</v>
       </c>
       <c r="T49">
-        <v>1.381137768248343</v>
+        <v>1.407698109945427</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05585556246698051</v>
+        <v>0.05469190491558508</v>
       </c>
       <c r="W49">
-        <v>0.222629258370286</v>
+        <v>0.222903648820905</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2792778123349025</v>
+        <v>0.2734595245779253</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1781283077543876</v>
+        <v>0.1800283077543876</v>
       </c>
       <c r="C50">
-        <v>-75.48644241614971</v>
+        <v>-88.05249399585381</v>
       </c>
       <c r="D50">
-        <v>296.5775575838503</v>
+        <v>292.3795060041462</v>
       </c>
       <c r="E50">
-        <v>386.4640000000001</v>
+        <v>394.8320000000001</v>
       </c>
       <c r="F50">
-        <v>401.664</v>
+        <v>410.032</v>
       </c>
       <c r="G50">
         <v>29.6</v>
@@ -5515,37 +5515,37 @@
         <v>25.9</v>
       </c>
       <c r="M50">
-        <v>94.71237120000002</v>
+        <v>96.68554560000001</v>
       </c>
       <c r="N50">
-        <v>-68.81237120000003</v>
+        <v>-70.78554560000001</v>
       </c>
       <c r="O50">
-        <v>-13.76247424000001</v>
+        <v>-14.15710912</v>
       </c>
       <c r="P50">
-        <v>-55.04989696000003</v>
+        <v>-56.62843648</v>
       </c>
       <c r="Q50">
-        <v>-49.64989696000002</v>
+        <v>-51.22843648</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1367972236929869</v>
+        <v>0.1385814829810847</v>
       </c>
       <c r="T50">
-        <v>1.407698109945427</v>
+        <v>1.435300033669847</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05469190491558508</v>
+        <v>0.05357574359077723</v>
       </c>
       <c r="W50">
-        <v>0.222903648820905</v>
+        <v>0.2231668396612947</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2734595245779253</v>
+        <v>0.2678787179538862</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1800283077543876</v>
+        <v>0.1819283077543876</v>
       </c>
       <c r="C51">
-        <v>-88.05249399585381</v>
+        <v>-100.5013576352533</v>
       </c>
       <c r="D51">
-        <v>292.3795060041462</v>
+        <v>288.2986423647467</v>
       </c>
       <c r="E51">
-        <v>394.8320000000001</v>
+        <v>403.2</v>
       </c>
       <c r="F51">
-        <v>410.032</v>
+        <v>418.4</v>
       </c>
       <c r="G51">
         <v>29.6</v>
@@ -5597,37 +5597,37 @@
         <v>25.9</v>
       </c>
       <c r="M51">
-        <v>96.68554560000001</v>
+        <v>98.65872000000002</v>
       </c>
       <c r="N51">
-        <v>-70.78554560000001</v>
+        <v>-72.75872000000001</v>
       </c>
       <c r="O51">
-        <v>-14.15710912</v>
+        <v>-14.551744</v>
       </c>
       <c r="P51">
-        <v>-56.62843648</v>
+        <v>-58.20697600000001</v>
       </c>
       <c r="Q51">
-        <v>-51.22843648</v>
+        <v>-52.80697600000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1385814829810847</v>
+        <v>0.1404371126407064</v>
       </c>
       <c r="T51">
-        <v>1.435300033669847</v>
+        <v>1.464006034343244</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05357574359077723</v>
+        <v>0.05250422871896168</v>
       </c>
       <c r="W51">
-        <v>0.2231668396612947</v>
+        <v>0.2234195028680689</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2678787179538862</v>
+        <v>0.2625211435948085</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1819283077543876</v>
+        <v>0.1838283077543876</v>
       </c>
       <c r="C52">
-        <v>-100.5013576352533</v>
+        <v>-112.8378727131005</v>
       </c>
       <c r="D52">
-        <v>288.2986423647467</v>
+        <v>284.3301272868995</v>
       </c>
       <c r="E52">
-        <v>403.2</v>
+        <v>411.568</v>
       </c>
       <c r="F52">
-        <v>418.4</v>
+        <v>426.768</v>
       </c>
       <c r="G52">
         <v>29.6</v>
@@ -5679,37 +5679,37 @@
         <v>25.9</v>
       </c>
       <c r="M52">
-        <v>98.65872000000002</v>
+        <v>100.6318944</v>
       </c>
       <c r="N52">
-        <v>-72.75872000000001</v>
+        <v>-74.73189440000002</v>
       </c>
       <c r="O52">
-        <v>-14.551744</v>
+        <v>-14.94637888</v>
       </c>
       <c r="P52">
-        <v>-58.20697600000001</v>
+        <v>-59.78551552000001</v>
       </c>
       <c r="Q52">
-        <v>-52.80697600000001</v>
+        <v>-54.38551552000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1404371126407064</v>
+        <v>0.1423684822864351</v>
       </c>
       <c r="T52">
-        <v>1.464006034343244</v>
+        <v>1.493883708513514</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05250422871896168</v>
+        <v>0.05147473403819774</v>
       </c>
       <c r="W52">
-        <v>0.2234195028680689</v>
+        <v>0.223662257713793</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2625211435948085</v>
+        <v>0.2573736701909886</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1838283077543876</v>
+        <v>0.1857283077543876</v>
       </c>
       <c r="C53">
-        <v>-112.8378727131005</v>
+        <v>-125.0666157644162</v>
       </c>
       <c r="D53">
-        <v>284.3301272868995</v>
+        <v>280.4693842355838</v>
       </c>
       <c r="E53">
-        <v>411.568</v>
+        <v>419.936</v>
       </c>
       <c r="F53">
-        <v>426.768</v>
+        <v>435.136</v>
       </c>
       <c r="G53">
         <v>29.6</v>
@@ -5761,37 +5761,37 @@
         <v>25.9</v>
       </c>
       <c r="M53">
-        <v>100.6318944</v>
+        <v>102.6050688</v>
       </c>
       <c r="N53">
-        <v>-74.73189440000002</v>
+        <v>-76.70506880000002</v>
       </c>
       <c r="O53">
-        <v>-14.94637888</v>
+        <v>-15.34101376</v>
       </c>
       <c r="P53">
-        <v>-59.78551552000001</v>
+        <v>-61.36405504000002</v>
       </c>
       <c r="Q53">
-        <v>-54.38551552000001</v>
+        <v>-55.96405504000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1423684822864351</v>
+        <v>0.1443803256674026</v>
       </c>
       <c r="T53">
-        <v>1.493883708513514</v>
+        <v>1.525006285774213</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05147473403819774</v>
+        <v>0.05048483530669393</v>
       </c>
       <c r="W53">
-        <v>0.223662257713793</v>
+        <v>0.2238956758346816</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2573736701909886</v>
+        <v>0.2524241765334696</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1857283077543876</v>
+        <v>0.1876283077543876</v>
       </c>
       <c r="C54">
-        <v>-125.0666157644162</v>
+        <v>-137.1919180863931</v>
       </c>
       <c r="D54">
-        <v>280.4693842355838</v>
+        <v>276.712081913607</v>
       </c>
       <c r="E54">
-        <v>419.936</v>
+        <v>428.3040000000001</v>
       </c>
       <c r="F54">
-        <v>435.136</v>
+        <v>443.5040000000001</v>
       </c>
       <c r="G54">
         <v>29.6</v>
@@ -5843,37 +5843,37 @@
         <v>25.9</v>
       </c>
       <c r="M54">
-        <v>102.6050688</v>
+        <v>104.5782432</v>
       </c>
       <c r="N54">
-        <v>-76.70506880000002</v>
+        <v>-78.67824320000003</v>
       </c>
       <c r="O54">
-        <v>-15.34101376</v>
+        <v>-15.73564864000001</v>
       </c>
       <c r="P54">
-        <v>-61.36405504000002</v>
+        <v>-62.94259456000002</v>
       </c>
       <c r="Q54">
-        <v>-55.96405504000002</v>
+        <v>-57.54259456000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1443803256674026</v>
+        <v>0.1464777794050068</v>
       </c>
       <c r="T54">
-        <v>1.525006285774213</v>
+        <v>1.557453228024728</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.05048483530669393</v>
+        <v>0.04953229124430347</v>
       </c>
       <c r="W54">
-        <v>0.2238956758346816</v>
+        <v>0.2241202857245932</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2524241765334696</v>
+        <v>0.2476614562215173</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1876283077543876</v>
+        <v>0.1895283077543876</v>
       </c>
       <c r="C55">
-        <v>-137.1919180863931</v>
+        <v>-149.2178819478635</v>
       </c>
       <c r="D55">
-        <v>276.712081913607</v>
+        <v>273.0541180521366</v>
       </c>
       <c r="E55">
-        <v>428.3040000000001</v>
+        <v>436.6720000000001</v>
       </c>
       <c r="F55">
-        <v>443.5040000000001</v>
+        <v>451.8720000000001</v>
       </c>
       <c r="G55">
         <v>29.6</v>
@@ -5925,37 +5925,37 @@
         <v>25.9</v>
       </c>
       <c r="M55">
-        <v>104.5782432</v>
+        <v>106.5514176</v>
       </c>
       <c r="N55">
-        <v>-78.67824320000003</v>
+        <v>-80.65141760000003</v>
       </c>
       <c r="O55">
-        <v>-15.73564864000001</v>
+        <v>-16.13028352000001</v>
       </c>
       <c r="P55">
-        <v>-62.94259456000002</v>
+        <v>-64.52113408000002</v>
       </c>
       <c r="Q55">
-        <v>-57.54259456000001</v>
+        <v>-59.12113408000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1464777794050068</v>
+        <v>0.1486664267833765</v>
       </c>
       <c r="T55">
-        <v>1.557453228024728</v>
+        <v>1.59131090689483</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04953229124430347</v>
+        <v>0.04861502659163119</v>
       </c>
       <c r="W55">
-        <v>0.2241202857245932</v>
+        <v>0.2243365767296934</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2476614562215173</v>
+        <v>0.2430751329581559</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1895283077543876</v>
+        <v>0.1914283077543876</v>
       </c>
       <c r="C56">
-        <v>-149.2178819478635</v>
+        <v>-161.1483955298661</v>
       </c>
       <c r="D56">
-        <v>273.0541180521366</v>
+        <v>269.491604470134</v>
       </c>
       <c r="E56">
-        <v>436.6720000000001</v>
+        <v>445.0400000000001</v>
       </c>
       <c r="F56">
-        <v>451.8720000000001</v>
+        <v>460.2400000000001</v>
       </c>
       <c r="G56">
         <v>29.6</v>
@@ -6007,37 +6007,37 @@
         <v>25.9</v>
       </c>
       <c r="M56">
-        <v>106.5514176</v>
+        <v>108.524592</v>
       </c>
       <c r="N56">
-        <v>-80.65141760000003</v>
+        <v>-82.62459200000004</v>
       </c>
       <c r="O56">
-        <v>-16.13028352000001</v>
+        <v>-16.52491840000001</v>
       </c>
       <c r="P56">
-        <v>-64.52113408000002</v>
+        <v>-66.09967360000003</v>
       </c>
       <c r="Q56">
-        <v>-59.12113408000002</v>
+        <v>-60.69967360000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1486664267833765</v>
+        <v>0.1509523473785627</v>
       </c>
       <c r="T56">
-        <v>1.59131090689483</v>
+        <v>1.626673371492493</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04861502659163119</v>
+        <v>0.04773111701723789</v>
       </c>
       <c r="W56">
-        <v>0.2243365767296934</v>
+        <v>0.2245450026073353</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2430751329581559</v>
+        <v>0.2386555850861893</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1914283077543876</v>
+        <v>0.1933283077543876</v>
       </c>
       <c r="C57">
-        <v>-161.1483955298661</v>
+        <v>-172.9871467117051</v>
       </c>
       <c r="D57">
-        <v>269.491604470134</v>
+        <v>266.0208532882949</v>
       </c>
       <c r="E57">
-        <v>445.0400000000001</v>
+        <v>453.4080000000001</v>
       </c>
       <c r="F57">
-        <v>460.2400000000001</v>
+        <v>468.6080000000001</v>
       </c>
       <c r="G57">
         <v>29.6</v>
@@ -6089,37 +6089,37 @@
         <v>25.9</v>
       </c>
       <c r="M57">
-        <v>108.524592</v>
+        <v>110.4977664</v>
       </c>
       <c r="N57">
-        <v>-82.62459200000004</v>
+        <v>-84.59776640000001</v>
       </c>
       <c r="O57">
-        <v>-16.52491840000001</v>
+        <v>-16.91955328</v>
       </c>
       <c r="P57">
-        <v>-66.09967360000003</v>
+        <v>-67.67821312000001</v>
       </c>
       <c r="Q57">
-        <v>-60.69967360000003</v>
+        <v>-62.27821312</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1509523473785627</v>
+        <v>0.1533421734553482</v>
       </c>
       <c r="T57">
-        <v>1.626673371492493</v>
+        <v>1.663643220844595</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04773111701723789</v>
+        <v>0.04687877564193008</v>
       </c>
       <c r="W57">
-        <v>0.2245450026073353</v>
+        <v>0.2247459847036329</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2386555850861893</v>
+        <v>0.2343938782096504</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1933283077543876</v>
+        <v>0.1952283077543877</v>
       </c>
       <c r="C58">
-        <v>-172.9871467117051</v>
+        <v>-184.7376358052613</v>
       </c>
       <c r="D58">
-        <v>266.0208532882949</v>
+        <v>262.6383641947388</v>
       </c>
       <c r="E58">
-        <v>453.4080000000001</v>
+        <v>461.7760000000001</v>
       </c>
       <c r="F58">
-        <v>468.6080000000001</v>
+        <v>476.9760000000001</v>
       </c>
       <c r="G58">
         <v>29.6</v>
@@ -6171,37 +6171,37 @@
         <v>25.9</v>
       </c>
       <c r="M58">
-        <v>110.4977664</v>
+        <v>112.4709408</v>
       </c>
       <c r="N58">
-        <v>-84.59776640000001</v>
+        <v>-86.57094080000005</v>
       </c>
       <c r="O58">
-        <v>-16.91955328</v>
+        <v>-17.31418816000001</v>
       </c>
       <c r="P58">
-        <v>-67.67821312000001</v>
+        <v>-69.25675264000003</v>
       </c>
       <c r="Q58">
-        <v>-62.27821312</v>
+        <v>-63.85675264000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1533421734553482</v>
+        <v>0.1558431542333796</v>
       </c>
       <c r="T58">
-        <v>1.663643220844595</v>
+        <v>1.70233259807354</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04687877564193008</v>
+        <v>0.04605634098154533</v>
       </c>
       <c r="W58">
-        <v>0.2247459847036329</v>
+        <v>0.2249399147965516</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2343938782096504</v>
+        <v>0.2302817049077266</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1952283077543877</v>
+        <v>0.1971283077543877</v>
       </c>
       <c r="C59">
-        <v>-184.7376358052613</v>
+        <v>-196.4031873299895</v>
       </c>
       <c r="D59">
-        <v>262.6383641947388</v>
+        <v>259.3408126700106</v>
       </c>
       <c r="E59">
-        <v>461.7760000000001</v>
+        <v>470.1440000000001</v>
       </c>
       <c r="F59">
-        <v>476.9760000000001</v>
+        <v>485.3440000000001</v>
       </c>
       <c r="G59">
         <v>29.6</v>
@@ -6253,37 +6253,37 @@
         <v>25.9</v>
       </c>
       <c r="M59">
-        <v>112.4709408</v>
+        <v>114.4441152</v>
       </c>
       <c r="N59">
-        <v>-86.57094080000005</v>
+        <v>-88.54411520000002</v>
       </c>
       <c r="O59">
-        <v>-17.31418816000001</v>
+        <v>-17.70882304000001</v>
       </c>
       <c r="P59">
-        <v>-69.25675264000003</v>
+        <v>-70.83529216000002</v>
       </c>
       <c r="Q59">
-        <v>-63.85675264000002</v>
+        <v>-65.43529216000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1558431542333796</v>
+        <v>0.1584632293341743</v>
       </c>
       <c r="T59">
-        <v>1.70233259807354</v>
+        <v>1.7428643265991</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04605634098154533</v>
+        <v>0.04526226613703593</v>
       </c>
       <c r="W59">
-        <v>0.2249399147965516</v>
+        <v>0.2251271576448869</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2302817049077266</v>
+        <v>0.2263113306851797</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1971283077543876</v>
+        <v>0.1990283077543876</v>
       </c>
       <c r="C60">
-        <v>-196.4031873299892</v>
+        <v>-207.9869609118711</v>
       </c>
       <c r="D60">
-        <v>259.3408126700107</v>
+        <v>256.1250390881289</v>
       </c>
       <c r="E60">
-        <v>470.144</v>
+        <v>478.512</v>
       </c>
       <c r="F60">
-        <v>485.344</v>
+        <v>493.712</v>
       </c>
       <c r="G60">
         <v>29.6</v>
@@ -6335,37 +6335,37 @@
         <v>25.9</v>
       </c>
       <c r="M60">
-        <v>114.4441152</v>
+        <v>116.4172896</v>
       </c>
       <c r="N60">
-        <v>-88.54411519999999</v>
+        <v>-90.5172896</v>
       </c>
       <c r="O60">
-        <v>-17.70882304</v>
+        <v>-18.10345792</v>
       </c>
       <c r="P60">
-        <v>-70.83529215999999</v>
+        <v>-72.41383168</v>
       </c>
       <c r="Q60">
-        <v>-65.43529215999999</v>
+        <v>-67.01383168</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1584632293341743</v>
+        <v>0.1612111129764712</v>
       </c>
       <c r="T60">
-        <v>1.7428643265991</v>
+        <v>1.785373212613712</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04526226613703594</v>
+        <v>0.04449510908386584</v>
       </c>
       <c r="W60">
-        <v>0.2251271576448869</v>
+        <v>0.2253080532780244</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2263113306851797</v>
+        <v>0.2224755454193292</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1990283077543876</v>
+        <v>0.2009283077543876</v>
       </c>
       <c r="C61">
-        <v>-207.9869609118711</v>
+        <v>-219.4919613814304</v>
       </c>
       <c r="D61">
-        <v>256.1250390881289</v>
+        <v>252.9880386185696</v>
       </c>
       <c r="E61">
-        <v>478.512</v>
+        <v>486.8800000000001</v>
       </c>
       <c r="F61">
-        <v>493.712</v>
+        <v>502.08</v>
       </c>
       <c r="G61">
         <v>29.6</v>
@@ -6417,37 +6417,37 @@
         <v>25.9</v>
       </c>
       <c r="M61">
-        <v>116.4172896</v>
+        <v>118.390464</v>
       </c>
       <c r="N61">
-        <v>-90.5172896</v>
+        <v>-92.490464</v>
       </c>
       <c r="O61">
-        <v>-18.10345792</v>
+        <v>-18.4980928</v>
       </c>
       <c r="P61">
-        <v>-72.41383168</v>
+        <v>-73.99237120000001</v>
       </c>
       <c r="Q61">
-        <v>-67.01383168</v>
+        <v>-68.5923712</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1612111129764712</v>
+        <v>0.164096390800883</v>
       </c>
       <c r="T61">
-        <v>1.785373212613712</v>
+        <v>1.830007542929054</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04449510908386584</v>
+        <v>0.04375352393246807</v>
       </c>
       <c r="W61">
-        <v>0.2253080532780244</v>
+        <v>0.225482919056724</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2224755454193292</v>
+        <v>0.2187676196623404</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2009283077543876</v>
+        <v>0.2028283077543876</v>
       </c>
       <c r="C62">
-        <v>-219.4919613814304</v>
+        <v>-230.9210481386482</v>
       </c>
       <c r="D62">
-        <v>252.9880386185696</v>
+        <v>249.9269518613518</v>
       </c>
       <c r="E62">
-        <v>486.8800000000001</v>
+        <v>495.248</v>
       </c>
       <c r="F62">
-        <v>502.08</v>
+        <v>510.448</v>
       </c>
       <c r="G62">
         <v>29.6</v>
@@ -6499,37 +6499,37 @@
         <v>25.9</v>
       </c>
       <c r="M62">
-        <v>118.390464</v>
+        <v>120.3636384</v>
       </c>
       <c r="N62">
-        <v>-92.490464</v>
+        <v>-94.46363840000001</v>
       </c>
       <c r="O62">
-        <v>-18.4980928</v>
+        <v>-18.89272768</v>
       </c>
       <c r="P62">
-        <v>-73.99237120000001</v>
+        <v>-75.57091072</v>
       </c>
       <c r="Q62">
-        <v>-68.5923712</v>
+        <v>-70.17091071999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.164096390800883</v>
+        <v>0.1671296315906492</v>
       </c>
       <c r="T62">
-        <v>1.830007542929054</v>
+        <v>1.876930813260569</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04375352393246807</v>
+        <v>0.04303625304832925</v>
       </c>
       <c r="W62">
-        <v>0.225482919056724</v>
+        <v>0.225652051531204</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2187676196623404</v>
+        <v>0.2151812652416463</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2028283077543876</v>
+        <v>0.2047283077543877</v>
       </c>
       <c r="C63">
-        <v>-230.9210481386482</v>
+        <v>-242.2769438461294</v>
       </c>
       <c r="D63">
-        <v>249.9269518613518</v>
+        <v>246.9390561538707</v>
       </c>
       <c r="E63">
-        <v>495.248</v>
+        <v>503.616</v>
       </c>
       <c r="F63">
-        <v>510.448</v>
+        <v>518.816</v>
       </c>
       <c r="G63">
         <v>29.6</v>
@@ -6581,37 +6581,37 @@
         <v>25.9</v>
       </c>
       <c r="M63">
-        <v>120.3636384</v>
+        <v>122.3368128</v>
       </c>
       <c r="N63">
-        <v>-94.46363840000001</v>
+        <v>-96.43681280000001</v>
       </c>
       <c r="O63">
-        <v>-18.89272768</v>
+        <v>-19.28736256000001</v>
       </c>
       <c r="P63">
-        <v>-75.57091072</v>
+        <v>-77.14945024000001</v>
       </c>
       <c r="Q63">
-        <v>-70.17091071999999</v>
+        <v>-71.74945024</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1671296315906492</v>
+        <v>0.1703225166325085</v>
       </c>
       <c r="T63">
-        <v>1.876930813260569</v>
+        <v>1.926323729399005</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04303625304832925</v>
+        <v>0.04234211993464652</v>
       </c>
       <c r="W63">
-        <v>0.225652051531204</v>
+        <v>0.2258157281194104</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2151812652416463</v>
+        <v>0.2117105996732326</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2047283077543877</v>
+        <v>0.2066283077543876</v>
       </c>
       <c r="C64">
-        <v>-242.2769438461294</v>
+        <v>-253.5622425060698</v>
       </c>
       <c r="D64">
-        <v>246.9390561538707</v>
+        <v>244.0217574939303</v>
       </c>
       <c r="E64">
-        <v>503.616</v>
+        <v>511.9840000000001</v>
       </c>
       <c r="F64">
-        <v>518.816</v>
+        <v>527.1840000000001</v>
       </c>
       <c r="G64">
         <v>29.6</v>
@@ -6663,37 +6663,37 @@
         <v>25.9</v>
       </c>
       <c r="M64">
-        <v>122.3368128</v>
+        <v>124.3099872</v>
       </c>
       <c r="N64">
-        <v>-96.43681280000001</v>
+        <v>-98.40998720000002</v>
       </c>
       <c r="O64">
-        <v>-19.28736256000001</v>
+        <v>-19.68199744</v>
       </c>
       <c r="P64">
-        <v>-77.14945024000001</v>
+        <v>-78.72798976000001</v>
       </c>
       <c r="Q64">
-        <v>-71.74945024</v>
+        <v>-73.32798976000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1703225166325085</v>
+        <v>0.1736879900550087</v>
       </c>
       <c r="T64">
-        <v>1.926323729399005</v>
+        <v>1.978386532896276</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04234211993464652</v>
+        <v>0.04167002279282673</v>
       </c>
       <c r="W64">
-        <v>0.2258157281194104</v>
+        <v>0.2259742086254515</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2117105996732326</v>
+        <v>0.2083501139641337</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2066283077543876</v>
+        <v>0.2085283077543876</v>
       </c>
       <c r="C65">
-        <v>-253.5622425060698</v>
+        <v>-264.7794169713893</v>
       </c>
       <c r="D65">
-        <v>244.0217574939303</v>
+        <v>241.1725830286107</v>
       </c>
       <c r="E65">
-        <v>511.9840000000001</v>
+        <v>520.352</v>
       </c>
       <c r="F65">
-        <v>527.1840000000001</v>
+        <v>535.552</v>
       </c>
       <c r="G65">
         <v>29.6</v>
@@ -6745,37 +6745,37 @@
         <v>25.9</v>
       </c>
       <c r="M65">
-        <v>124.3099872</v>
+        <v>126.2831616</v>
       </c>
       <c r="N65">
-        <v>-98.40998720000002</v>
+        <v>-100.3831616</v>
       </c>
       <c r="O65">
-        <v>-19.68199744</v>
+        <v>-20.07663232000001</v>
       </c>
       <c r="P65">
-        <v>-78.72798976000001</v>
+        <v>-80.30652928000002</v>
       </c>
       <c r="Q65">
-        <v>-73.32798976000001</v>
+        <v>-74.90652928000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1736879900550087</v>
+        <v>0.1772404342232034</v>
       </c>
       <c r="T65">
-        <v>1.978386532896276</v>
+        <v>2.033341714365617</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04167002279282673</v>
+        <v>0.04101892868668881</v>
       </c>
       <c r="W65">
-        <v>0.2259742086254515</v>
+        <v>0.2261277366156788</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2083501139641337</v>
+        <v>0.205094643433444</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2085283077543876</v>
+        <v>0.2104283077543876</v>
       </c>
       <c r="C66">
-        <v>-264.7794169713893</v>
+        <v>-275.9308259367418</v>
       </c>
       <c r="D66">
-        <v>241.1725830286107</v>
+        <v>238.3891740632583</v>
       </c>
       <c r="E66">
-        <v>520.352</v>
+        <v>528.72</v>
       </c>
       <c r="F66">
-        <v>535.552</v>
+        <v>543.9200000000001</v>
       </c>
       <c r="G66">
         <v>29.6</v>
@@ -6827,37 +6827,37 @@
         <v>25.9</v>
       </c>
       <c r="M66">
-        <v>126.2831616</v>
+        <v>128.256336</v>
       </c>
       <c r="N66">
-        <v>-100.3831616</v>
+        <v>-102.356336</v>
       </c>
       <c r="O66">
-        <v>-20.07663232000001</v>
+        <v>-20.47126720000001</v>
       </c>
       <c r="P66">
-        <v>-80.30652928000002</v>
+        <v>-81.88506880000003</v>
       </c>
       <c r="Q66">
-        <v>-74.90652928000002</v>
+        <v>-76.48506880000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1772404342232034</v>
+        <v>0.1809958752010092</v>
       </c>
       <c r="T66">
-        <v>2.033341714365617</v>
+        <v>2.09143719191892</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04101892868668881</v>
+        <v>0.04038786824535514</v>
       </c>
       <c r="W66">
-        <v>0.2261277366156788</v>
+        <v>0.2262765406677453</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.205094643433444</v>
+        <v>0.2019393412267757</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2104283077543876</v>
+        <v>0.2123283077543876</v>
       </c>
       <c r="C67">
-        <v>-275.9308259367418</v>
+        <v>-287.0187204509419</v>
       </c>
       <c r="D67">
-        <v>238.3891740632583</v>
+        <v>235.6692795490582</v>
       </c>
       <c r="E67">
-        <v>528.72</v>
+        <v>537.0880000000001</v>
       </c>
       <c r="F67">
-        <v>543.9200000000001</v>
+        <v>552.2880000000001</v>
       </c>
       <c r="G67">
         <v>29.6</v>
@@ -6909,37 +6909,37 @@
         <v>25.9</v>
       </c>
       <c r="M67">
-        <v>128.256336</v>
+        <v>130.2295104</v>
       </c>
       <c r="N67">
-        <v>-102.356336</v>
+        <v>-104.3295104</v>
       </c>
       <c r="O67">
-        <v>-20.47126720000001</v>
+        <v>-20.86590208000001</v>
       </c>
       <c r="P67">
-        <v>-81.88506880000003</v>
+        <v>-83.46360832000002</v>
       </c>
       <c r="Q67">
-        <v>-76.48506880000002</v>
+        <v>-78.06360832000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1809958752010092</v>
+        <v>0.1849722244716271</v>
       </c>
       <c r="T67">
-        <v>2.09143719191892</v>
+        <v>2.15295005050477</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04038786824535514</v>
+        <v>0.03977593084769824</v>
       </c>
       <c r="W67">
-        <v>0.2262765406677453</v>
+        <v>0.2264208355061127</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2019393412267757</v>
+        <v>0.1988796542384912</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2123283077543876</v>
+        <v>0.2142283077543876</v>
       </c>
       <c r="C68">
-        <v>-287.0187204509419</v>
+        <v>-298.0452499886024</v>
       </c>
       <c r="D68">
-        <v>235.6692795490582</v>
+        <v>233.0107500113976</v>
       </c>
       <c r="E68">
-        <v>537.0880000000001</v>
+        <v>545.456</v>
       </c>
       <c r="F68">
-        <v>552.2880000000001</v>
+        <v>560.6560000000001</v>
       </c>
       <c r="G68">
         <v>29.6</v>
@@ -6991,37 +6991,37 @@
         <v>25.9</v>
       </c>
       <c r="M68">
-        <v>130.2295104</v>
+        <v>132.2026848</v>
       </c>
       <c r="N68">
-        <v>-104.3295104</v>
+        <v>-106.3026848</v>
       </c>
       <c r="O68">
-        <v>-20.86590208000001</v>
+        <v>-21.26053696</v>
       </c>
       <c r="P68">
-        <v>-83.46360832000002</v>
+        <v>-85.04214784000001</v>
       </c>
       <c r="Q68">
-        <v>-78.06360832000001</v>
+        <v>-79.64214784000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1849722244716271</v>
+        <v>0.189189564607131</v>
       </c>
       <c r="T68">
-        <v>2.15295005050477</v>
+        <v>2.218190961126127</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03977593084769824</v>
+        <v>0.03918226023803111</v>
       </c>
       <c r="W68">
-        <v>0.2264208355061127</v>
+        <v>0.2265608230358723</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1988796542384912</v>
+        <v>0.1959113011901555</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2142283077543876</v>
+        <v>0.2161283077543877</v>
       </c>
       <c r="C69">
-        <v>-298.0452499886024</v>
+        <v>-309.0124681153982</v>
       </c>
       <c r="D69">
-        <v>233.0107500113976</v>
+        <v>230.4115318846019</v>
       </c>
       <c r="E69">
-        <v>545.456</v>
+        <v>553.8240000000001</v>
       </c>
       <c r="F69">
-        <v>560.6560000000001</v>
+        <v>569.0240000000001</v>
       </c>
       <c r="G69">
         <v>29.6</v>
@@ -7073,37 +7073,37 @@
         <v>25.9</v>
       </c>
       <c r="M69">
-        <v>132.2026848</v>
+        <v>134.1758592</v>
       </c>
       <c r="N69">
-        <v>-106.3026848</v>
+        <v>-108.2758592</v>
       </c>
       <c r="O69">
-        <v>-21.26053696</v>
+        <v>-21.65517184</v>
       </c>
       <c r="P69">
-        <v>-85.04214784000001</v>
+        <v>-86.62068736000001</v>
       </c>
       <c r="Q69">
-        <v>-79.64214784000001</v>
+        <v>-81.22068736</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.189189564607131</v>
+        <v>0.1936704885011038</v>
       </c>
       <c r="T69">
-        <v>2.218190961126127</v>
+        <v>2.287509428661318</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03918226023803111</v>
+        <v>0.03860605052864829</v>
       </c>
       <c r="W69">
-        <v>0.2265608230358723</v>
+        <v>0.2266966932853448</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1959113011901555</v>
+        <v>0.1930302526432415</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2161283077543877</v>
+        <v>0.2180283077543877</v>
       </c>
       <c r="C70">
-        <v>-309.0124681153982</v>
+        <v>-319.9223377783404</v>
       </c>
       <c r="D70">
-        <v>230.4115318846019</v>
+        <v>227.8696622216597</v>
       </c>
       <c r="E70">
-        <v>553.8240000000001</v>
+        <v>562.192</v>
       </c>
       <c r="F70">
-        <v>569.0240000000001</v>
+        <v>577.3920000000001</v>
       </c>
       <c r="G70">
         <v>29.6</v>
@@ -7155,37 +7155,37 @@
         <v>25.9</v>
       </c>
       <c r="M70">
-        <v>134.1758592</v>
+        <v>136.1490336</v>
       </c>
       <c r="N70">
-        <v>-108.2758592</v>
+        <v>-110.2490336</v>
       </c>
       <c r="O70">
-        <v>-21.65517184</v>
+        <v>-22.04980672000001</v>
       </c>
       <c r="P70">
-        <v>-86.62068736000001</v>
+        <v>-88.19922688000001</v>
       </c>
       <c r="Q70">
-        <v>-81.22068736</v>
+        <v>-82.79922688000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1936704885011038</v>
+        <v>0.198440504259204</v>
       </c>
       <c r="T70">
-        <v>2.287509428661318</v>
+        <v>2.361300055392329</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03860605052864829</v>
+        <v>0.03804654254997223</v>
       </c>
       <c r="W70">
-        <v>0.2266966932853448</v>
+        <v>0.2268286252667166</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1930302526432415</v>
+        <v>0.1902327127498612</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2180283077543877</v>
+        <v>0.2199283077543876</v>
       </c>
       <c r="C71">
-        <v>-319.9223377783404</v>
+        <v>-330.7767362497012</v>
       </c>
       <c r="D71">
-        <v>227.8696622216597</v>
+        <v>225.3832637502989</v>
       </c>
       <c r="E71">
-        <v>562.192</v>
+        <v>570.5600000000001</v>
       </c>
       <c r="F71">
-        <v>577.3920000000001</v>
+        <v>585.7600000000001</v>
       </c>
       <c r="G71">
         <v>29.6</v>
@@ -7237,37 +7237,37 @@
         <v>25.9</v>
       </c>
       <c r="M71">
-        <v>136.1490336</v>
+        <v>138.122208</v>
       </c>
       <c r="N71">
-        <v>-110.2490336</v>
+        <v>-112.222208</v>
       </c>
       <c r="O71">
-        <v>-22.04980672000001</v>
+        <v>-22.4444416</v>
       </c>
       <c r="P71">
-        <v>-88.19922688000001</v>
+        <v>-89.77776640000002</v>
       </c>
       <c r="Q71">
-        <v>-82.79922688000001</v>
+        <v>-84.37776640000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.198440504259204</v>
+        <v>0.2035285210678441</v>
       </c>
       <c r="T71">
-        <v>2.361300055392329</v>
+        <v>2.44001005723874</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03804654254997223</v>
+        <v>0.03750302051354406</v>
       </c>
       <c r="W71">
-        <v>0.2268286252667166</v>
+        <v>0.2269567877629063</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1902327127498612</v>
+        <v>0.1875151025677203</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2199283077543876</v>
+        <v>0.2218283077543877</v>
       </c>
       <c r="C72">
-        <v>-330.7767362497012</v>
+        <v>-341.5774597507593</v>
       </c>
       <c r="D72">
-        <v>225.3832637502989</v>
+        <v>222.9505402492408</v>
       </c>
       <c r="E72">
-        <v>570.5600000000001</v>
+        <v>578.9280000000001</v>
       </c>
       <c r="F72">
-        <v>585.7600000000001</v>
+        <v>594.1280000000002</v>
       </c>
       <c r="G72">
         <v>29.6</v>
@@ -7319,37 +7319,37 @@
         <v>25.9</v>
       </c>
       <c r="M72">
-        <v>138.122208</v>
+        <v>140.0953824</v>
       </c>
       <c r="N72">
-        <v>-112.222208</v>
+        <v>-114.1953824</v>
       </c>
       <c r="O72">
-        <v>-22.4444416</v>
+        <v>-22.83907648000001</v>
       </c>
       <c r="P72">
-        <v>-89.77776640000002</v>
+        <v>-91.35630592000003</v>
       </c>
       <c r="Q72">
-        <v>-84.37776640000001</v>
+        <v>-85.95630592000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2035285210678441</v>
+        <v>0.2089674355874249</v>
       </c>
       <c r="T72">
-        <v>2.44001005723874</v>
+        <v>2.524148335074559</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03750302051354406</v>
+        <v>0.03697480895701526</v>
       </c>
       <c r="W72">
-        <v>0.2269567877629063</v>
+        <v>0.2270813400479358</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1875151025677203</v>
+        <v>0.1848740447850764</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2218283077543876</v>
+        <v>0.2237283077543876</v>
       </c>
       <c r="C73">
-        <v>-341.5774597507591</v>
+        <v>-352.3262277792973</v>
       </c>
       <c r="D73">
-        <v>222.9505402492409</v>
+        <v>220.5697722207027</v>
       </c>
       <c r="E73">
-        <v>578.928</v>
+        <v>587.2959999999999</v>
       </c>
       <c r="F73">
-        <v>594.128</v>
+        <v>602.496</v>
       </c>
       <c r="G73">
         <v>29.6</v>
@@ -7401,37 +7401,37 @@
         <v>25.9</v>
       </c>
       <c r="M73">
-        <v>140.0953824</v>
+        <v>142.0685568</v>
       </c>
       <c r="N73">
-        <v>-114.1953824</v>
+        <v>-116.1685568</v>
       </c>
       <c r="O73">
-        <v>-22.83907648</v>
+        <v>-23.23371136</v>
       </c>
       <c r="P73">
-        <v>-91.35630592</v>
+        <v>-92.93484544</v>
       </c>
       <c r="Q73">
-        <v>-85.95630591999999</v>
+        <v>-87.53484544</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2089674355874249</v>
+        <v>0.2147948440012615</v>
       </c>
       <c r="T73">
-        <v>2.524148335074558</v>
+        <v>2.61429648989865</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03697480895701527</v>
+        <v>0.03646126994372339</v>
       </c>
       <c r="W73">
-        <v>0.2270813400479358</v>
+        <v>0.22720243254727</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1848740447850764</v>
+        <v>0.182306349718617</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2237283077543876</v>
+        <v>0.2256283077543876</v>
       </c>
       <c r="C74">
-        <v>-352.3262277792973</v>
+        <v>-363.0246871627651</v>
       </c>
       <c r="D74">
-        <v>220.5697722207027</v>
+        <v>218.239312837235</v>
       </c>
       <c r="E74">
-        <v>587.2959999999999</v>
+        <v>595.664</v>
       </c>
       <c r="F74">
-        <v>602.496</v>
+        <v>610.864</v>
       </c>
       <c r="G74">
         <v>29.6</v>
@@ -7483,37 +7483,37 @@
         <v>25.9</v>
       </c>
       <c r="M74">
-        <v>142.0685568</v>
+        <v>144.0417312</v>
       </c>
       <c r="N74">
-        <v>-116.1685568</v>
+        <v>-118.1417312</v>
       </c>
       <c r="O74">
-        <v>-23.23371136</v>
+        <v>-23.62834624</v>
       </c>
       <c r="P74">
-        <v>-92.93484544</v>
+        <v>-94.51338496000001</v>
       </c>
       <c r="Q74">
-        <v>-87.53484544</v>
+        <v>-89.11338496</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2147948440012615</v>
+        <v>0.2210539122976045</v>
       </c>
       <c r="T74">
-        <v>2.61429648989865</v>
+        <v>2.711122285820821</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03646126994372339</v>
+        <v>0.03596180049243951</v>
       </c>
       <c r="W74">
-        <v>0.22720243254727</v>
+        <v>0.2273202074438828</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.182306349718617</v>
+        <v>0.1798090024621976</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2256283077543876</v>
+        <v>0.2275283077543876</v>
       </c>
       <c r="C75">
-        <v>-363.0246871627651</v>
+        <v>-373.6744158571805</v>
       </c>
       <c r="D75">
-        <v>218.239312837235</v>
+        <v>215.9575841428196</v>
       </c>
       <c r="E75">
-        <v>595.664</v>
+        <v>604.032</v>
       </c>
       <c r="F75">
-        <v>610.864</v>
+        <v>619.2320000000001</v>
       </c>
       <c r="G75">
         <v>29.6</v>
@@ -7565,37 +7565,37 @@
         <v>25.9</v>
       </c>
       <c r="M75">
-        <v>144.0417312</v>
+        <v>146.0149056</v>
       </c>
       <c r="N75">
-        <v>-118.1417312</v>
+        <v>-120.1149056</v>
       </c>
       <c r="O75">
-        <v>-23.62834624</v>
+        <v>-24.02298112</v>
       </c>
       <c r="P75">
-        <v>-94.51338496000001</v>
+        <v>-96.09192448000002</v>
       </c>
       <c r="Q75">
-        <v>-89.11338496</v>
+        <v>-90.69192448000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2210539122976045</v>
+        <v>0.2277944473859738</v>
       </c>
       <c r="T75">
-        <v>2.711122285820821</v>
+        <v>2.815396219890853</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03596180049243951</v>
+        <v>0.03547583021551465</v>
       </c>
       <c r="W75">
-        <v>0.2273202074438828</v>
+        <v>0.2274347992351816</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1798090024621976</v>
+        <v>0.1773791510775733</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2275283077543876</v>
+        <v>0.2294283077543876</v>
       </c>
       <c r="C76">
-        <v>-373.6744158571805</v>
+        <v>-384.2769265101904</v>
       </c>
       <c r="D76">
-        <v>215.9575841428196</v>
+        <v>213.7230734898097</v>
       </c>
       <c r="E76">
-        <v>604.032</v>
+        <v>612.4</v>
       </c>
       <c r="F76">
-        <v>619.2320000000001</v>
+        <v>627.6</v>
       </c>
       <c r="G76">
         <v>29.6</v>
@@ -7647,37 +7647,37 @@
         <v>25.9</v>
       </c>
       <c r="M76">
-        <v>146.0149056</v>
+        <v>147.98808</v>
       </c>
       <c r="N76">
-        <v>-120.1149056</v>
+        <v>-122.08808</v>
       </c>
       <c r="O76">
-        <v>-24.02298112</v>
+        <v>-24.41761600000001</v>
       </c>
       <c r="P76">
-        <v>-96.09192448000002</v>
+        <v>-97.67046400000001</v>
       </c>
       <c r="Q76">
-        <v>-90.69192448000001</v>
+        <v>-92.270464</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2277944473859738</v>
+        <v>0.2350742252814128</v>
       </c>
       <c r="T76">
-        <v>2.815396219890853</v>
+        <v>2.928012068686487</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03547583021551465</v>
+        <v>0.03500281914597445</v>
       </c>
       <c r="W76">
-        <v>0.2274347992351816</v>
+        <v>0.2275463352453792</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1773791510775733</v>
+        <v>0.1750140957298723</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2294283077543876</v>
+        <v>0.2313283077543876</v>
       </c>
       <c r="C77">
-        <v>-384.2769265101904</v>
+        <v>-394.8336698051933</v>
       </c>
       <c r="D77">
-        <v>213.7230734898097</v>
+        <v>211.5343301948068</v>
       </c>
       <c r="E77">
-        <v>612.4</v>
+        <v>620.768</v>
       </c>
       <c r="F77">
-        <v>627.6</v>
+        <v>635.9680000000001</v>
       </c>
       <c r="G77">
         <v>29.6</v>
@@ -7729,37 +7729,37 @@
         <v>25.9</v>
       </c>
       <c r="M77">
-        <v>147.98808</v>
+        <v>149.9612544</v>
       </c>
       <c r="N77">
-        <v>-122.08808</v>
+        <v>-124.0612544</v>
       </c>
       <c r="O77">
-        <v>-24.41761600000001</v>
+        <v>-24.81225088000001</v>
       </c>
       <c r="P77">
-        <v>-97.67046400000001</v>
+        <v>-99.24900352000002</v>
       </c>
       <c r="Q77">
-        <v>-92.270464</v>
+        <v>-93.84900352000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2350742252814128</v>
+        <v>0.2429606513348051</v>
       </c>
       <c r="T77">
-        <v>2.928012068686487</v>
+        <v>3.050012571548425</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03500281914597445</v>
+        <v>0.034542255736159</v>
       </c>
       <c r="W77">
-        <v>0.2275463352453792</v>
+        <v>0.2276549360974137</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1750140957298723</v>
+        <v>0.1727112786807951</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2313283077543876</v>
+        <v>0.2332283077543876</v>
       </c>
       <c r="C78">
-        <v>-394.8336698051933</v>
+        <v>-405.346037602062</v>
       </c>
       <c r="D78">
-        <v>211.5343301948068</v>
+        <v>209.389962397938</v>
       </c>
       <c r="E78">
-        <v>620.768</v>
+        <v>629.136</v>
       </c>
       <c r="F78">
-        <v>635.9680000000001</v>
+        <v>644.336</v>
       </c>
       <c r="G78">
         <v>29.6</v>
@@ -7811,37 +7811,37 @@
         <v>25.9</v>
       </c>
       <c r="M78">
-        <v>149.9612544</v>
+        <v>151.9344288</v>
       </c>
       <c r="N78">
-        <v>-124.0612544</v>
+        <v>-126.0344288</v>
       </c>
       <c r="O78">
-        <v>-24.81225088000001</v>
+        <v>-25.20688576</v>
       </c>
       <c r="P78">
-        <v>-99.24900352000002</v>
+        <v>-100.82754304</v>
       </c>
       <c r="Q78">
-        <v>-93.84900352000001</v>
+        <v>-95.42754303999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2429606513348051</v>
+        <v>0.2515328535667531</v>
       </c>
       <c r="T78">
-        <v>3.050012571548425</v>
+        <v>3.182621813789661</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.034542255736159</v>
+        <v>0.03409365501231278</v>
       </c>
       <c r="W78">
-        <v>0.2276549360974137</v>
+        <v>0.2277607161480966</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1727112786807951</v>
+        <v>0.1704682750615639</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2332283077543876</v>
+        <v>0.2351283077543876</v>
       </c>
       <c r="C79">
-        <v>-405.346037602062</v>
+        <v>-415.8153658887555</v>
       </c>
       <c r="D79">
-        <v>209.389962397938</v>
+        <v>207.2886341112446</v>
       </c>
       <c r="E79">
-        <v>629.136</v>
+        <v>637.504</v>
       </c>
       <c r="F79">
-        <v>644.336</v>
+        <v>652.7040000000001</v>
       </c>
       <c r="G79">
         <v>29.6</v>
@@ -7893,37 +7893,37 @@
         <v>25.9</v>
       </c>
       <c r="M79">
-        <v>151.9344288</v>
+        <v>153.9076032</v>
       </c>
       <c r="N79">
-        <v>-126.0344288</v>
+        <v>-128.0076032</v>
       </c>
       <c r="O79">
-        <v>-25.20688576</v>
+        <v>-25.60152064</v>
       </c>
       <c r="P79">
-        <v>-100.82754304</v>
+        <v>-102.40608256</v>
       </c>
       <c r="Q79">
-        <v>-95.42754303999999</v>
+        <v>-97.00608256</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2515328535667531</v>
+        <v>0.2608843469106964</v>
       </c>
       <c r="T79">
-        <v>3.182621813789661</v>
+        <v>3.32728644168919</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03409365501231278</v>
+        <v>0.03365655687112928</v>
       </c>
       <c r="W79">
-        <v>0.2277607161480966</v>
+        <v>0.2278637838897877</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1704682750615639</v>
+        <v>0.1682827843556465</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2351283077543876</v>
+        <v>0.2370283077543877</v>
       </c>
       <c r="C80">
-        <v>-415.8153658887555</v>
+        <v>-426.2429375569692</v>
       </c>
       <c r="D80">
-        <v>207.2886341112446</v>
+        <v>205.229062443031</v>
       </c>
       <c r="E80">
-        <v>637.504</v>
+        <v>645.8720000000001</v>
       </c>
       <c r="F80">
-        <v>652.7040000000001</v>
+        <v>661.0720000000001</v>
       </c>
       <c r="G80">
         <v>29.6</v>
@@ -7975,37 +7975,37 @@
         <v>25.9</v>
       </c>
       <c r="M80">
-        <v>153.9076032</v>
+        <v>155.8807776</v>
       </c>
       <c r="N80">
-        <v>-128.0076032</v>
+        <v>-129.9807776</v>
       </c>
       <c r="O80">
-        <v>-25.60152064</v>
+        <v>-25.99615552000001</v>
       </c>
       <c r="P80">
-        <v>-102.40608256</v>
+        <v>-103.98462208</v>
       </c>
       <c r="Q80">
-        <v>-97.00608256</v>
+        <v>-98.58462208000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2608843469106964</v>
+        <v>0.2711264586683487</v>
       </c>
       <c r="T80">
-        <v>3.32728644168919</v>
+        <v>3.4857286531982</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03365655687112928</v>
+        <v>0.03323052450567195</v>
       </c>
       <c r="W80">
-        <v>0.2278637838897877</v>
+        <v>0.2279642423215626</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1682827843556465</v>
+        <v>0.1661526225283597</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2370283077543877</v>
+        <v>0.2389283077543876</v>
       </c>
       <c r="C81">
-        <v>-426.2429375569692</v>
+        <v>-436.629985013946</v>
       </c>
       <c r="D81">
-        <v>205.229062443031</v>
+        <v>203.2100149860541</v>
       </c>
       <c r="E81">
-        <v>645.8720000000001</v>
+        <v>654.24</v>
       </c>
       <c r="F81">
-        <v>661.0720000000001</v>
+        <v>669.4400000000001</v>
       </c>
       <c r="G81">
         <v>29.6</v>
@@ -8057,37 +8057,37 @@
         <v>25.9</v>
       </c>
       <c r="M81">
-        <v>155.8807776</v>
+        <v>157.853952</v>
       </c>
       <c r="N81">
-        <v>-129.9807776</v>
+        <v>-131.953952</v>
       </c>
       <c r="O81">
-        <v>-25.99615552000001</v>
+        <v>-26.3907904</v>
       </c>
       <c r="P81">
-        <v>-103.98462208</v>
+        <v>-105.5631616</v>
       </c>
       <c r="Q81">
-        <v>-98.58462208000003</v>
+        <v>-100.1631616</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2711264586683487</v>
+        <v>0.2823927816017661</v>
       </c>
       <c r="T81">
-        <v>3.4857286531982</v>
+        <v>3.66001508585811</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03323052450567195</v>
+        <v>0.03281514294935105</v>
       </c>
       <c r="W81">
-        <v>0.2279642423215626</v>
+        <v>0.228062189292543</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1661526225283597</v>
+        <v>0.1640757147467553</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2389283077543876</v>
+        <v>0.2408283077543876</v>
       </c>
       <c r="C82">
-        <v>-436.629985013946</v>
+        <v>-446.977692641619</v>
       </c>
       <c r="D82">
-        <v>203.2100149860541</v>
+        <v>201.2303073583811</v>
       </c>
       <c r="E82">
-        <v>654.24</v>
+        <v>662.6080000000001</v>
       </c>
       <c r="F82">
-        <v>669.4400000000001</v>
+        <v>677.8080000000001</v>
       </c>
       <c r="G82">
         <v>29.6</v>
@@ -8139,37 +8139,37 @@
         <v>25.9</v>
       </c>
       <c r="M82">
-        <v>157.853952</v>
+        <v>159.8271264</v>
       </c>
       <c r="N82">
-        <v>-131.953952</v>
+        <v>-133.9271264</v>
       </c>
       <c r="O82">
-        <v>-26.3907904</v>
+        <v>-26.78542528000001</v>
       </c>
       <c r="P82">
-        <v>-105.5631616</v>
+        <v>-107.14170112</v>
       </c>
       <c r="Q82">
-        <v>-100.1631616</v>
+        <v>-101.74170112</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2823927816017661</v>
+        <v>0.2948450332650169</v>
       </c>
       <c r="T82">
-        <v>3.66001508585811</v>
+        <v>3.852647458798011</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03281514294935105</v>
+        <v>0.03241001772775412</v>
       </c>
       <c r="W82">
-        <v>0.228062189292543</v>
+        <v>0.2281577178197956</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1640757147467553</v>
+        <v>0.1620500886387707</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2408283077543876</v>
+        <v>0.2427283077543876</v>
       </c>
       <c r="C83">
-        <v>-446.977692641619</v>
+        <v>-457.2871991133944</v>
       </c>
       <c r="D83">
-        <v>201.2303073583811</v>
+        <v>199.2888008866057</v>
       </c>
       <c r="E83">
-        <v>662.6080000000001</v>
+        <v>670.9760000000001</v>
       </c>
       <c r="F83">
-        <v>677.8080000000001</v>
+        <v>686.1760000000002</v>
       </c>
       <c r="G83">
         <v>29.6</v>
@@ -8221,37 +8221,37 @@
         <v>25.9</v>
       </c>
       <c r="M83">
-        <v>159.8271264</v>
+        <v>161.8003008</v>
       </c>
       <c r="N83">
-        <v>-133.9271264</v>
+        <v>-135.9003008</v>
       </c>
       <c r="O83">
-        <v>-26.78542528000001</v>
+        <v>-27.18006016000001</v>
       </c>
       <c r="P83">
-        <v>-107.14170112</v>
+        <v>-108.72024064</v>
       </c>
       <c r="Q83">
-        <v>-101.74170112</v>
+        <v>-103.32024064</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2948450332650169</v>
+        <v>0.3086808684464068</v>
       </c>
       <c r="T83">
-        <v>3.852647458798011</v>
+        <v>4.066683428731234</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03241001772775412</v>
+        <v>0.03201477360912298</v>
       </c>
       <c r="W83">
-        <v>0.2281577178197956</v>
+        <v>0.2282509163829688</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1620500886387707</v>
+        <v>0.160073868045615</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2427283077543876</v>
+        <v>0.2446283077543877</v>
       </c>
       <c r="C84">
-        <v>-457.2871991133944</v>
+        <v>-467.5595995781024</v>
       </c>
       <c r="D84">
-        <v>199.2888008866057</v>
+        <v>197.3844004218977</v>
       </c>
       <c r="E84">
-        <v>670.9760000000001</v>
+        <v>679.3440000000001</v>
       </c>
       <c r="F84">
-        <v>686.1760000000002</v>
+        <v>694.5440000000001</v>
       </c>
       <c r="G84">
         <v>29.6</v>
@@ -8303,37 +8303,37 @@
         <v>25.9</v>
       </c>
       <c r="M84">
-        <v>161.8003008</v>
+        <v>163.7734752</v>
       </c>
       <c r="N84">
-        <v>-135.9003008</v>
+        <v>-137.8734752</v>
       </c>
       <c r="O84">
-        <v>-27.18006016000001</v>
+        <v>-27.57469504000001</v>
       </c>
       <c r="P84">
-        <v>-108.72024064</v>
+        <v>-110.29878016</v>
       </c>
       <c r="Q84">
-        <v>-103.32024064</v>
+        <v>-104.89878016</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3086808684464068</v>
+        <v>0.3241444489432543</v>
       </c>
       <c r="T84">
-        <v>4.066683428731234</v>
+        <v>4.305900101009542</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03201477360912298</v>
+        <v>0.03162905344515764</v>
       </c>
       <c r="W84">
-        <v>0.2282509163829688</v>
+        <v>0.2283418691976318</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.160073868045615</v>
+        <v>0.1581452672257883</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2446283077543877</v>
+        <v>0.2465283077543877</v>
       </c>
       <c r="C85">
-        <v>-467.5595995781024</v>
+        <v>-477.7959477199125</v>
       </c>
       <c r="D85">
-        <v>197.3844004218977</v>
+        <v>195.5160522800876</v>
       </c>
       <c r="E85">
-        <v>679.3440000000001</v>
+        <v>687.7120000000001</v>
       </c>
       <c r="F85">
-        <v>694.5440000000001</v>
+        <v>702.9120000000001</v>
       </c>
       <c r="G85">
         <v>29.6</v>
@@ -8385,37 +8385,37 @@
         <v>25.9</v>
       </c>
       <c r="M85">
-        <v>163.7734752</v>
+        <v>165.7466496</v>
       </c>
       <c r="N85">
-        <v>-137.8734752</v>
+        <v>-139.8466496</v>
       </c>
       <c r="O85">
-        <v>-27.57469504000001</v>
+        <v>-27.96932992000001</v>
       </c>
       <c r="P85">
-        <v>-110.29878016</v>
+        <v>-111.87731968</v>
       </c>
       <c r="Q85">
-        <v>-104.89878016</v>
+        <v>-106.47731968</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3241444489432543</v>
+        <v>0.3415409770022078</v>
       </c>
       <c r="T85">
-        <v>4.305900101009542</v>
+        <v>4.57501885732264</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03162905344515764</v>
+        <v>0.03125251709462004</v>
       </c>
       <c r="W85">
-        <v>0.2283418691976318</v>
+        <v>0.2284306564690886</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1581452672257883</v>
+        <v>0.1562625854731002</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2465283077543876</v>
+        <v>0.2484283077543877</v>
       </c>
       <c r="C86">
-        <v>-477.7959477199124</v>
+        <v>-487.997257702358</v>
       </c>
       <c r="D86">
-        <v>195.5160522800876</v>
+        <v>193.6827422976421</v>
       </c>
       <c r="E86">
-        <v>687.712</v>
+        <v>696.08</v>
       </c>
       <c r="F86">
-        <v>702.912</v>
+        <v>711.2800000000001</v>
       </c>
       <c r="G86">
         <v>29.6</v>
@@ -8467,37 +8467,37 @@
         <v>25.9</v>
       </c>
       <c r="M86">
-        <v>165.7466496</v>
+        <v>167.719824</v>
       </c>
       <c r="N86">
-        <v>-139.8466496</v>
+        <v>-141.819824</v>
       </c>
       <c r="O86">
-        <v>-27.96932992</v>
+        <v>-28.36396480000001</v>
       </c>
       <c r="P86">
-        <v>-111.87731968</v>
+        <v>-113.4558592</v>
       </c>
       <c r="Q86">
-        <v>-106.47731968</v>
+        <v>-108.0558592</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3415409770022075</v>
+        <v>0.361257042135688</v>
       </c>
       <c r="T86">
-        <v>4.575018857322636</v>
+        <v>4.880020114477479</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03125251709462005</v>
+        <v>0.03088484042291864</v>
       </c>
       <c r="W86">
-        <v>0.2284306564690886</v>
+        <v>0.2285173546282758</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1562625854731002</v>
+        <v>0.1544242021145932</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2484283077543877</v>
+        <v>0.2503283077543876</v>
       </c>
       <c r="C87">
-        <v>-487.997257702358</v>
+        <v>-498.1645060040035</v>
       </c>
       <c r="D87">
-        <v>193.6827422976421</v>
+        <v>191.8834939959965</v>
       </c>
       <c r="E87">
-        <v>696.08</v>
+        <v>704.448</v>
       </c>
       <c r="F87">
-        <v>711.2800000000001</v>
+        <v>719.648</v>
       </c>
       <c r="G87">
         <v>29.6</v>
@@ -8549,37 +8549,37 @@
         <v>25.9</v>
       </c>
       <c r="M87">
-        <v>167.719824</v>
+        <v>169.6929984</v>
       </c>
       <c r="N87">
-        <v>-141.819824</v>
+        <v>-143.7929984</v>
       </c>
       <c r="O87">
-        <v>-28.36396480000001</v>
+        <v>-28.75859968</v>
       </c>
       <c r="P87">
-        <v>-113.4558592</v>
+        <v>-115.03439872</v>
       </c>
       <c r="Q87">
-        <v>-108.0558592</v>
+        <v>-109.63439872</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.361257042135688</v>
+        <v>0.3837896880025229</v>
       </c>
       <c r="T87">
-        <v>4.880020114477479</v>
+        <v>5.228592979797299</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03088484042291864</v>
+        <v>0.03052571437148935</v>
       </c>
       <c r="W87">
-        <v>0.2285173546282758</v>
+        <v>0.2286020365512028</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1544242021145932</v>
+        <v>0.1526285718574468</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2503283077543876</v>
+        <v>0.2522283077543876</v>
       </c>
       <c r="C88">
-        <v>-498.1645060040035</v>
+        <v>-508.2986331527384</v>
       </c>
       <c r="D88">
-        <v>191.8834939959965</v>
+        <v>190.1173668472617</v>
       </c>
       <c r="E88">
-        <v>704.448</v>
+        <v>712.816</v>
       </c>
       <c r="F88">
-        <v>719.648</v>
+        <v>728.0160000000001</v>
       </c>
       <c r="G88">
         <v>29.6</v>
@@ -8631,37 +8631,37 @@
         <v>25.9</v>
       </c>
       <c r="M88">
-        <v>169.6929984</v>
+        <v>171.6661728</v>
       </c>
       <c r="N88">
-        <v>-143.7929984</v>
+        <v>-145.7661728</v>
       </c>
       <c r="O88">
-        <v>-28.75859968</v>
+        <v>-29.15323456</v>
       </c>
       <c r="P88">
-        <v>-115.03439872</v>
+        <v>-116.61293824</v>
       </c>
       <c r="Q88">
-        <v>-109.63439872</v>
+        <v>-111.21293824</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3837896880025229</v>
+        <v>0.4097888947719477</v>
       </c>
       <c r="T88">
-        <v>5.228592979797299</v>
+        <v>5.630792439781706</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03052571437148935</v>
+        <v>0.03017484409135729</v>
       </c>
       <c r="W88">
-        <v>0.2286020365512028</v>
+        <v>0.228684771763258</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1526285718574468</v>
+        <v>0.1508742204567864</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2522283077543876</v>
+        <v>0.2541283077543877</v>
       </c>
       <c r="C89">
-        <v>-508.2986331527384</v>
+        <v>-518.4005453651663</v>
       </c>
       <c r="D89">
-        <v>190.1173668472617</v>
+        <v>188.3834546348337</v>
       </c>
       <c r="E89">
-        <v>712.816</v>
+        <v>721.184</v>
       </c>
       <c r="F89">
-        <v>728.0160000000001</v>
+        <v>736.384</v>
       </c>
       <c r="G89">
         <v>29.6</v>
@@ -8713,37 +8713,37 @@
         <v>25.9</v>
       </c>
       <c r="M89">
-        <v>171.6661728</v>
+        <v>173.6393472</v>
       </c>
       <c r="N89">
-        <v>-145.7661728</v>
+        <v>-147.7393472</v>
       </c>
       <c r="O89">
-        <v>-29.15323456</v>
+        <v>-29.54786944</v>
       </c>
       <c r="P89">
-        <v>-116.61293824</v>
+        <v>-118.19147776</v>
       </c>
       <c r="Q89">
-        <v>-111.21293824</v>
+        <v>-112.79147776</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4097888947719477</v>
+        <v>0.4401213026696101</v>
       </c>
       <c r="T89">
-        <v>5.630792439781706</v>
+        <v>6.10002514309685</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03017484409135729</v>
+        <v>0.02983194813577368</v>
       </c>
       <c r="W89">
-        <v>0.228684771763258</v>
+        <v>0.2287656266295846</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1508742204567864</v>
+        <v>0.1491597406788685</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2541283077543877</v>
+        <v>0.2560283077543876</v>
       </c>
       <c r="C90">
-        <v>-518.4005453651663</v>
+        <v>-528.4711160970982</v>
       </c>
       <c r="D90">
-        <v>188.3834546348337</v>
+        <v>186.6808839029019</v>
       </c>
       <c r="E90">
-        <v>721.184</v>
+        <v>729.552</v>
       </c>
       <c r="F90">
-        <v>736.384</v>
+        <v>744.7520000000001</v>
       </c>
       <c r="G90">
         <v>29.6</v>
@@ -8795,37 +8795,37 @@
         <v>25.9</v>
       </c>
       <c r="M90">
-        <v>173.6393472</v>
+        <v>175.6125216</v>
       </c>
       <c r="N90">
-        <v>-147.7393472</v>
+        <v>-149.7125216</v>
       </c>
       <c r="O90">
-        <v>-29.54786944</v>
+        <v>-29.94250432000001</v>
       </c>
       <c r="P90">
-        <v>-118.19147776</v>
+        <v>-119.77001728</v>
       </c>
       <c r="Q90">
-        <v>-112.79147776</v>
+        <v>-114.37001728</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4401213026696101</v>
+        <v>0.4759686938213928</v>
       </c>
       <c r="T90">
-        <v>6.10002514309685</v>
+        <v>6.65457288337838</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02983194813577368</v>
+        <v>0.02949675770728184</v>
       </c>
       <c r="W90">
-        <v>0.2287656266295846</v>
+        <v>0.2288446645326229</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1491597406788685</v>
+        <v>0.1474837885364092</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2560283077543876</v>
+        <v>0.2579283077543876</v>
       </c>
       <c r="C91">
-        <v>-528.4711160970982</v>
+        <v>-538.5111875107174</v>
       </c>
       <c r="D91">
-        <v>186.6808839029019</v>
+        <v>185.0088124892828</v>
       </c>
       <c r="E91">
-        <v>729.552</v>
+        <v>737.9200000000001</v>
       </c>
       <c r="F91">
-        <v>744.7520000000001</v>
+        <v>753.1200000000001</v>
       </c>
       <c r="G91">
         <v>29.6</v>
@@ -8877,37 +8877,37 @@
         <v>25.9</v>
       </c>
       <c r="M91">
-        <v>175.6125216</v>
+        <v>177.585696</v>
       </c>
       <c r="N91">
-        <v>-149.7125216</v>
+        <v>-151.685696</v>
       </c>
       <c r="O91">
-        <v>-29.94250432000001</v>
+        <v>-30.33713920000001</v>
       </c>
       <c r="P91">
-        <v>-119.77001728</v>
+        <v>-121.3485568</v>
       </c>
       <c r="Q91">
-        <v>-114.37001728</v>
+        <v>-115.9485568</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4759686938213928</v>
+        <v>0.5189855632035322</v>
       </c>
       <c r="T91">
-        <v>6.65457288337838</v>
+        <v>7.32003017171622</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02949675770728184</v>
+        <v>0.02916901595497871</v>
       </c>
       <c r="W91">
-        <v>0.2288446645326229</v>
+        <v>0.228921946037816</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1474837885364092</v>
+        <v>0.1458450797748936</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2579283077543876</v>
+        <v>0.2598283077543876</v>
       </c>
       <c r="C92">
-        <v>-538.5111875107174</v>
+        <v>-548.5215718635993</v>
       </c>
       <c r="D92">
-        <v>185.0088124892828</v>
+        <v>183.3664281364007</v>
       </c>
       <c r="E92">
-        <v>737.9200000000001</v>
+        <v>746.288</v>
       </c>
       <c r="F92">
-        <v>753.1200000000001</v>
+        <v>761.4880000000001</v>
       </c>
       <c r="G92">
         <v>29.6</v>
@@ -8959,37 +8959,37 @@
         <v>25.9</v>
       </c>
       <c r="M92">
-        <v>177.585696</v>
+        <v>179.5588704</v>
       </c>
       <c r="N92">
-        <v>-151.685696</v>
+        <v>-153.6588704</v>
       </c>
       <c r="O92">
-        <v>-30.33713920000001</v>
+        <v>-30.73177408</v>
       </c>
       <c r="P92">
-        <v>-121.3485568</v>
+        <v>-122.92709632</v>
       </c>
       <c r="Q92">
-        <v>-115.9485568</v>
+        <v>-117.52709632</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5189855632035322</v>
+        <v>0.5715617368928135</v>
       </c>
       <c r="T92">
-        <v>7.32003017171622</v>
+        <v>8.133366857462468</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02916901595497871</v>
+        <v>0.02884847731811082</v>
       </c>
       <c r="W92">
-        <v>0.228921946037816</v>
+        <v>0.2289975290483895</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1458450797748936</v>
+        <v>0.1442423865905541</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2598283077543876</v>
+        <v>0.2617283077543877</v>
       </c>
       <c r="C93">
-        <v>-548.5215718635993</v>
+        <v>-558.5030528243981</v>
       </c>
       <c r="D93">
-        <v>183.3664281364007</v>
+        <v>181.7529471756021</v>
       </c>
       <c r="E93">
-        <v>746.288</v>
+        <v>754.6560000000001</v>
       </c>
       <c r="F93">
-        <v>761.4880000000001</v>
+        <v>769.8560000000001</v>
       </c>
       <c r="G93">
         <v>29.6</v>
@@ -9041,37 +9041,37 @@
         <v>25.9</v>
       </c>
       <c r="M93">
-        <v>179.5588704</v>
+        <v>181.5320448</v>
       </c>
       <c r="N93">
-        <v>-153.6588704</v>
+        <v>-155.6320448</v>
       </c>
       <c r="O93">
-        <v>-30.73177408</v>
+        <v>-31.12640896000001</v>
       </c>
       <c r="P93">
-        <v>-122.92709632</v>
+        <v>-124.50563584</v>
       </c>
       <c r="Q93">
-        <v>-117.52709632</v>
+        <v>-119.10563584</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5715617368928135</v>
+        <v>0.6372819540044155</v>
       </c>
       <c r="T93">
-        <v>8.133366857462468</v>
+        <v>9.150037714645279</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02884847731811082</v>
+        <v>0.02853490691247917</v>
       </c>
       <c r="W93">
-        <v>0.2289975290483895</v>
+        <v>0.2290714689500374</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1442423865905541</v>
+        <v>0.1426745345623959</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2617283077543877</v>
+        <v>0.2636283077543877</v>
       </c>
       <c r="C94">
-        <v>-558.5030528243981</v>
+        <v>-568.4563867196741</v>
       </c>
       <c r="D94">
-        <v>181.7529471756021</v>
+        <v>180.1676132803261</v>
       </c>
       <c r="E94">
-        <v>754.6560000000001</v>
+        <v>763.0240000000001</v>
       </c>
       <c r="F94">
-        <v>769.8560000000001</v>
+        <v>778.2240000000002</v>
       </c>
       <c r="G94">
         <v>29.6</v>
@@ -9123,37 +9123,37 @@
         <v>25.9</v>
       </c>
       <c r="M94">
-        <v>181.5320448</v>
+        <v>183.5052192000001</v>
       </c>
       <c r="N94">
-        <v>-155.6320448</v>
+        <v>-157.6052192000001</v>
       </c>
       <c r="O94">
-        <v>-31.12640896000001</v>
+        <v>-31.52104384000001</v>
       </c>
       <c r="P94">
-        <v>-124.50563584</v>
+        <v>-126.08417536</v>
       </c>
       <c r="Q94">
-        <v>-119.10563584</v>
+        <v>-120.68417536</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6372819540044155</v>
+        <v>0.7217793760050463</v>
       </c>
       <c r="T94">
-        <v>9.150037714645279</v>
+        <v>10.45718595959461</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02853490691247917</v>
+        <v>0.02822807995643101</v>
       </c>
       <c r="W94">
-        <v>0.2290714689500374</v>
+        <v>0.2291438187462736</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1426745345623959</v>
+        <v>0.1411403997821551</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2636283077543877</v>
+        <v>0.2655283077543877</v>
       </c>
       <c r="C95">
-        <v>-568.4563867196741</v>
+        <v>-578.382303716037</v>
       </c>
       <c r="D95">
-        <v>180.1676132803261</v>
+        <v>178.6096962839632</v>
       </c>
       <c r="E95">
-        <v>763.0240000000001</v>
+        <v>771.3920000000001</v>
       </c>
       <c r="F95">
-        <v>778.2240000000002</v>
+        <v>786.5920000000001</v>
       </c>
       <c r="G95">
         <v>29.6</v>
@@ -9205,37 +9205,37 @@
         <v>25.9</v>
       </c>
       <c r="M95">
-        <v>183.5052192000001</v>
+        <v>185.4783936</v>
       </c>
       <c r="N95">
-        <v>-157.6052192000001</v>
+        <v>-159.5783936</v>
       </c>
       <c r="O95">
-        <v>-31.52104384000001</v>
+        <v>-31.91567872000001</v>
       </c>
       <c r="P95">
-        <v>-126.08417536</v>
+        <v>-127.66271488</v>
       </c>
       <c r="Q95">
-        <v>-120.68417536</v>
+        <v>-122.26271488</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7217793760050463</v>
+        <v>0.8344426053392209</v>
       </c>
       <c r="T95">
-        <v>10.45718595959461</v>
+        <v>12.20005028619371</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02822807995643101</v>
+        <v>0.02792778123349026</v>
       </c>
       <c r="W95">
-        <v>0.2291438187462736</v>
+        <v>0.229214629185143</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1411403997821551</v>
+        <v>0.1396389061674513</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2655283077543877</v>
+        <v>0.2674283077543876</v>
       </c>
       <c r="C96">
-        <v>-578.382303716037</v>
+        <v>-588.2815089414796</v>
       </c>
       <c r="D96">
-        <v>178.6096962839632</v>
+        <v>177.0784910585205</v>
       </c>
       <c r="E96">
-        <v>771.3920000000001</v>
+        <v>779.7600000000001</v>
       </c>
       <c r="F96">
-        <v>786.5920000000001</v>
+        <v>794.9600000000002</v>
       </c>
       <c r="G96">
         <v>29.6</v>
@@ -9287,37 +9287,37 @@
         <v>25.9</v>
       </c>
       <c r="M96">
-        <v>185.4783936</v>
+        <v>187.451568</v>
       </c>
       <c r="N96">
-        <v>-159.5783936</v>
+        <v>-161.551568</v>
       </c>
       <c r="O96">
-        <v>-31.91567872000001</v>
+        <v>-32.31031360000001</v>
       </c>
       <c r="P96">
-        <v>-127.66271488</v>
+        <v>-129.2412544</v>
       </c>
       <c r="Q96">
-        <v>-122.26271488</v>
+        <v>-123.8412544</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8344426053392209</v>
+        <v>0.9921711264070655</v>
       </c>
       <c r="T96">
-        <v>12.20005028619371</v>
+        <v>14.64006034343246</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02792778123349026</v>
+        <v>0.0276338045889272</v>
       </c>
       <c r="W96">
-        <v>0.229214629185143</v>
+        <v>0.229283948877931</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1396389061674513</v>
+        <v>0.1381690229446361</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2674283077543876</v>
+        <v>0.2693283077543877</v>
       </c>
       <c r="C97">
-        <v>-588.2815089414796</v>
+        <v>-598.1546835495246</v>
       </c>
       <c r="D97">
-        <v>177.0784910585205</v>
+        <v>175.5733164504754</v>
       </c>
       <c r="E97">
-        <v>779.7600000000001</v>
+        <v>788.128</v>
       </c>
       <c r="F97">
-        <v>794.9600000000002</v>
+        <v>803.3280000000001</v>
       </c>
       <c r="G97">
         <v>29.6</v>
@@ -9369,37 +9369,37 @@
         <v>25.9</v>
       </c>
       <c r="M97">
-        <v>187.451568</v>
+        <v>189.4247424</v>
       </c>
       <c r="N97">
-        <v>-161.551568</v>
+        <v>-163.5247424</v>
       </c>
       <c r="O97">
-        <v>-32.31031360000001</v>
+        <v>-32.70494848000001</v>
       </c>
       <c r="P97">
-        <v>-129.2412544</v>
+        <v>-130.81979392</v>
       </c>
       <c r="Q97">
-        <v>-123.8412544</v>
+        <v>-125.41979392</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9921711264070655</v>
+        <v>1.228763908008832</v>
       </c>
       <c r="T97">
-        <v>14.64006034343246</v>
+        <v>18.30007542929058</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0276338045889272</v>
+        <v>0.02734595245779254</v>
       </c>
       <c r="W97">
-        <v>0.229283948877931</v>
+        <v>0.2293518244104525</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1381690229446361</v>
+        <v>0.1367297622889627</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2693283077543876</v>
+        <v>0.2712283077543877</v>
       </c>
       <c r="C98">
-        <v>-598.1546835495246</v>
+        <v>-608.0024857295567</v>
       </c>
       <c r="D98">
-        <v>175.5733164504755</v>
+        <v>174.0935142704433</v>
       </c>
       <c r="E98">
-        <v>788.128</v>
+        <v>796.496</v>
       </c>
       <c r="F98">
-        <v>803.3280000000001</v>
+        <v>811.696</v>
       </c>
       <c r="G98">
         <v>29.6</v>
@@ -9451,37 +9451,37 @@
         <v>25.9</v>
       </c>
       <c r="M98">
-        <v>189.4247424</v>
+        <v>191.3979168</v>
       </c>
       <c r="N98">
-        <v>-163.5247424</v>
+        <v>-165.4979168</v>
       </c>
       <c r="O98">
-        <v>-32.70494848000001</v>
+        <v>-33.09958336</v>
       </c>
       <c r="P98">
-        <v>-130.81979392</v>
+        <v>-132.39833344</v>
       </c>
       <c r="Q98">
-        <v>-125.41979392</v>
+        <v>-126.99833344</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.228763908008829</v>
+        <v>1.623085210678439</v>
       </c>
       <c r="T98">
-        <v>18.30007542929053</v>
+        <v>24.40010057238738</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02734595245779254</v>
+        <v>0.02706403542214519</v>
       </c>
       <c r="W98">
-        <v>0.2293518244104525</v>
+        <v>0.2294183004474582</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1367297622889627</v>
+        <v>0.135320177110726</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2712283077543877</v>
+        <v>0.2731283077543876</v>
       </c>
       <c r="C99">
-        <v>-608.0024857295567</v>
+        <v>-617.825551666489</v>
       </c>
       <c r="D99">
-        <v>174.0935142704433</v>
+        <v>172.6384483335111</v>
       </c>
       <c r="E99">
-        <v>796.496</v>
+        <v>804.864</v>
       </c>
       <c r="F99">
-        <v>811.696</v>
+        <v>820.0640000000001</v>
       </c>
       <c r="G99">
         <v>29.6</v>
@@ -9533,37 +9533,37 @@
         <v>25.9</v>
       </c>
       <c r="M99">
-        <v>191.3979168</v>
+        <v>193.3710912</v>
       </c>
       <c r="N99">
-        <v>-165.4979168</v>
+        <v>-167.4710912</v>
       </c>
       <c r="O99">
-        <v>-33.09958336</v>
+        <v>-33.49421824</v>
       </c>
       <c r="P99">
-        <v>-132.39833344</v>
+        <v>-133.97687296</v>
       </c>
       <c r="Q99">
-        <v>-126.99833344</v>
+        <v>-128.57687296</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.623085210678439</v>
+        <v>2.411727816017658</v>
       </c>
       <c r="T99">
-        <v>24.40010057238738</v>
+        <v>36.60015085858106</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02706403542214519</v>
+        <v>0.02678787179538861</v>
       </c>
       <c r="W99">
-        <v>0.2294183004474582</v>
+        <v>0.2294834198306474</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.135320177110726</v>
+        <v>0.1339393589769431</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2731283077543876</v>
+        <v>0.2750283077543876</v>
       </c>
       <c r="C100">
-        <v>-617.825551666489</v>
+        <v>-627.6244964527023</v>
       </c>
       <c r="D100">
-        <v>172.6384483335111</v>
+        <v>171.2075035472977</v>
       </c>
       <c r="E100">
-        <v>804.864</v>
+        <v>813.232</v>
       </c>
       <c r="F100">
-        <v>820.0640000000001</v>
+        <v>828.432</v>
       </c>
       <c r="G100">
         <v>29.6</v>
@@ -9615,37 +9615,37 @@
         <v>25.9</v>
       </c>
       <c r="M100">
-        <v>193.3710912</v>
+        <v>195.3442656</v>
       </c>
       <c r="N100">
-        <v>-167.4710912</v>
+        <v>-169.4442656</v>
       </c>
       <c r="O100">
-        <v>-33.49421824</v>
+        <v>-33.88885312</v>
       </c>
       <c r="P100">
-        <v>-133.97687296</v>
+        <v>-135.55541248</v>
       </c>
       <c r="Q100">
-        <v>-128.57687296</v>
+        <v>-130.15541248</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.411727816017658</v>
+        <v>4.777655632035318</v>
       </c>
       <c r="T100">
-        <v>36.60015085858106</v>
+        <v>73.20030171716213</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02678787179538861</v>
+        <v>0.02651728723179883</v>
       </c>
       <c r="W100">
-        <v>0.2294834198306474</v>
+        <v>0.2295472236707418</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1339393589769431</v>
+        <v>0.1325864361589942</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2750283077543876</v>
-      </c>
-      <c r="C101">
-        <v>-627.6244964527023</v>
-      </c>
-      <c r="D101">
-        <v>171.2075035472977</v>
-      </c>
-      <c r="E101">
-        <v>813.232</v>
-      </c>
-      <c r="F101">
-        <v>828.432</v>
-      </c>
-      <c r="G101">
-        <v>29.6</v>
-      </c>
-      <c r="H101">
-        <v>821.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.3</v>
-      </c>
-      <c r="K101">
-        <v>5.400000000000002</v>
-      </c>
-      <c r="L101">
-        <v>25.9</v>
-      </c>
-      <c r="M101">
-        <v>195.3442656</v>
-      </c>
-      <c r="N101">
-        <v>-169.4442656</v>
-      </c>
-      <c r="O101">
-        <v>-33.88885312</v>
-      </c>
-      <c r="P101">
-        <v>-135.55541248</v>
-      </c>
-      <c r="Q101">
-        <v>-130.15541248</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.777655632035318</v>
-      </c>
-      <c r="T101">
-        <v>73.20030171716213</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02651728723179883</v>
-      </c>
-      <c r="W101">
-        <v>0.2295472236707418</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1325864361589942</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
